--- a/sup_tables/sup_table_s13_replication_timing_83.xlsx
+++ b/sup_tables/sup_table_s13_replication_timing_83.xlsx
@@ -621,19 +621,19 @@
         <v>465.333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000485708744815494</v>
+        <v>0.0000485708744815496</v>
       </c>
       <c r="E4" t="n">
         <v>912.739393939393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000376792113090973</v>
+        <v>0.000376792113090972</v>
       </c>
       <c r="G4" t="n">
         <v>168.713068548467</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0589571602323704</v>
+        <v>0.0589571602323708</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -656,13 +656,13 @@
         <v>1466.73333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000163483776225036</v>
+        <v>0.000163483776225035</v>
       </c>
       <c r="G5" t="n">
-        <v>70.9507024274173</v>
+        <v>70.9507024274174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.709265915484786</v>
+        <v>0.709265915484785</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
@@ -679,7 +679,7 @@
         <v>240.551515151515</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00015197094430228</v>
+        <v>0.000151970944302278</v>
       </c>
       <c r="E6" t="n">
         <v>601.696969696969</v>
@@ -688,10 +688,10 @@
         <v>0.000240640556751395</v>
       </c>
       <c r="G6" t="n">
-        <v>46.0932684300561</v>
+        <v>46.0932684300563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.358199053721751</v>
+        <v>0.358199053721749</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
@@ -714,13 +714,13 @@
         <v>4042.6303030303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000492910089522338</v>
+        <v>0.000492910089522337</v>
       </c>
       <c r="G7" t="n">
         <v>685.46852663644</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00000244063340786227</v>
+        <v>0.00000244063340786224</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
@@ -746,10 +746,10 @@
         <v>0.000134611663469459</v>
       </c>
       <c r="G8" t="n">
-        <v>82.8558342419188</v>
+        <v>82.8558342419191</v>
       </c>
       <c r="H8" t="n">
-        <v>0.587180608563431</v>
+        <v>0.58718060856343</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -766,7 +766,7 @@
         <v>5493.41818181818</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000096927209452201</v>
+        <v>0.0000969272094522012</v>
       </c>
       <c r="E9" t="n">
         <v>12447.2424242424</v>
@@ -778,7 +778,7 @@
         <v>1131.54216294644</v>
       </c>
       <c r="H9" t="n">
-        <v>0.357473085582618</v>
+        <v>0.357473085582619</v>
       </c>
       <c r="I9" t="s">
         <v>11</v>
@@ -795,7 +795,7 @@
         <v>1158.44242424242</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000577290511145542</v>
+        <v>0.0000577290511145543</v>
       </c>
       <c r="E10" t="n">
         <v>2236.7696969697</v>
@@ -824,7 +824,7 @@
         <v>374.187878787879</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000980299547863686</v>
+        <v>0.0000980299547863681</v>
       </c>
       <c r="E11" t="n">
         <v>658.866666666667</v>
@@ -836,7 +836,7 @@
         <v>135.353295288946</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0376989638609042</v>
+        <v>0.0376989638609039</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -859,13 +859,13 @@
         <v>364.533333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000279693615536694</v>
+        <v>0.000279693615536696</v>
       </c>
       <c r="G12" t="n">
-        <v>20.7051087754607</v>
+        <v>20.7051087754606</v>
       </c>
       <c r="H12" t="n">
-        <v>0.538223578937879</v>
+        <v>0.538223578937878</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -882,19 +882,19 @@
         <v>959.260606060606</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0000671979156296126</v>
+        <v>0.0000671979156296122</v>
       </c>
       <c r="E13" t="n">
         <v>1679.00606060606</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000641043801743817</v>
+        <v>0.000641043801743818</v>
       </c>
       <c r="G13" t="n">
-        <v>349.95931420581</v>
+        <v>349.959314205811</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0376403238807205</v>
+        <v>0.03764032388072</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -911,7 +911,7 @@
         <v>1681.13939393939</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000561606257974066</v>
+        <v>0.0000561606257974069</v>
       </c>
       <c r="E14" t="n">
         <v>3854.34545454546</v>
@@ -920,7 +920,7 @@
         <v>0.000252006189331814</v>
       </c>
       <c r="G14" t="n">
-        <v>510.183889474041</v>
+        <v>510.183889474042</v>
       </c>
       <c r="H14" t="n">
         <v>0.114646482276452</v>
@@ -949,7 +949,7 @@
         <v>0.000161794150784486</v>
       </c>
       <c r="G15" t="n">
-        <v>6.44410334847319</v>
+        <v>6.4441033484732</v>
       </c>
       <c r="H15" t="n">
         <v>0.974238343008097</v>
@@ -969,16 +969,16 @@
         <v>19.230303030303</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000704593893943384</v>
+        <v>0.000704593893943382</v>
       </c>
       <c r="E16" t="n">
-        <v>40.260606060606</v>
+        <v>40.2606060606061</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000216038934990136</v>
+        <v>0.000216038934990135</v>
       </c>
       <c r="G16" t="n">
-        <v>5.87552708673019</v>
+        <v>5.8755270867302</v>
       </c>
       <c r="H16" t="n">
         <v>0.472553601250674</v>
@@ -998,7 +998,7 @@
         <v>776.145454545454</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000799997064772648</v>
+        <v>0.000079999706477265</v>
       </c>
       <c r="E17" t="n">
         <v>1944.48484848485</v>
@@ -1010,7 +1010,7 @@
         <v>186.2287856658</v>
       </c>
       <c r="H17" t="n">
-        <v>0.149115210065284</v>
+        <v>0.149115210065285</v>
       </c>
       <c r="I17" t="s">
         <v>11</v>
@@ -1033,13 +1033,13 @@
         <v>960.48484848485</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000580068312072644</v>
+        <v>0.000580068312072641</v>
       </c>
       <c r="G18" t="n">
         <v>145.163163559442</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0112226424751325</v>
+        <v>0.0112226424751326</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
@@ -1068,7 +1068,7 @@
         <v>640.328574047939</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0080649162523885</v>
+        <v>0.00806491625238852</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
@@ -1097,7 +1097,7 @@
         <v>1174.00911460409</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0164940734338567</v>
+        <v>0.0164940734338566</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
@@ -1117,16 +1117,16 @@
         <v>0.000157595515373089</v>
       </c>
       <c r="E21" t="n">
-        <v>846.442424242424</v>
+        <v>846.442424242425</v>
       </c>
       <c r="F21" t="n">
-        <v>0.000892975791814258</v>
+        <v>0.000892975791814251</v>
       </c>
       <c r="G21" t="n">
-        <v>99.4318807923751</v>
+        <v>99.4318807923753</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0752977735233663</v>
+        <v>0.0752977735233678</v>
       </c>
       <c r="I21" t="s">
         <v>11</v>
@@ -1146,13 +1146,13 @@
         <v>0.0000626300950906213</v>
       </c>
       <c r="E22" t="n">
-        <v>673.472727272728</v>
+        <v>673.472727272727</v>
       </c>
       <c r="F22" t="n">
-        <v>0.000214775268258403</v>
+        <v>0.000214775268258404</v>
       </c>
       <c r="G22" t="n">
-        <v>98.5364082341418</v>
+        <v>98.5364082341415</v>
       </c>
       <c r="H22" t="n">
         <v>0.158985907181925</v>
@@ -1172,16 +1172,16 @@
         <v>25.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000129517684454771</v>
+        <v>0.00012951768445477</v>
       </c>
       <c r="E23" t="n">
         <v>80.4545454545455</v>
       </c>
       <c r="F23" t="n">
-        <v>0.000299496227752714</v>
+        <v>0.000299496227752713</v>
       </c>
       <c r="G23" t="n">
-        <v>6.95978306876648</v>
+        <v>6.95978306876649</v>
       </c>
       <c r="H23" t="n">
         <v>0.234688815318284</v>
@@ -1201,7 +1201,7 @@
         <v>243.109090909091</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0000196620769977232</v>
+        <v>0.000019662076997723</v>
       </c>
       <c r="E24" t="n">
         <v>614.072727272727</v>
@@ -1213,7 +1213,7 @@
         <v>109.688550781116</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0175872155524738</v>
+        <v>0.0175872155524735</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
@@ -1236,13 +1236,13 @@
         <v>4122.64242424243</v>
       </c>
       <c r="F25" t="n">
-        <v>0.107720278231466</v>
+        <v>0.107720278231465</v>
       </c>
       <c r="G25" t="n">
         <v>627.909096154415</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0000925062441218099</v>
+        <v>0.000092506244121813</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -1262,7 +1262,7 @@
         <v>0.000304169701530535</v>
       </c>
       <c r="E26" t="n">
-        <v>3655.64848484847</v>
+        <v>3655.64848484848</v>
       </c>
       <c r="F26" t="n">
         <v>0.122235617065621</v>
@@ -1271,7 +1271,7 @@
         <v>830.915451681264</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00000540493032395704</v>
+        <v>0.0000054049303239571</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
@@ -1288,7 +1288,7 @@
         <v>39.5151515151515</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000179889550664451</v>
+        <v>0.00017988955066445</v>
       </c>
       <c r="E27" t="n">
         <v>44.1636363636364</v>
@@ -1300,7 +1300,7 @@
         <v>30.1530702892857</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000619926830617899</v>
+        <v>0.000619926830617898</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
@@ -1320,16 +1320,16 @@
         <v>0.0000459437238947418</v>
       </c>
       <c r="E28" t="n">
-        <v>9240.70303030304</v>
+        <v>9240.70303030301</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0580181411698065</v>
+        <v>0.0580181411698072</v>
       </c>
       <c r="G28" t="n">
         <v>2223.94444650997</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0000677112004244623</v>
+        <v>0.000067711200424463</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
@@ -1346,7 +1346,7 @@
         <v>101.551515151515</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00000581578299652022</v>
+        <v>0.00000581578299652018</v>
       </c>
       <c r="E29" t="n">
         <v>186.20606060606</v>
@@ -1375,10 +1375,10 @@
         <v>22459.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000444094720620456</v>
+        <v>0.000444094720620457</v>
       </c>
       <c r="E30" t="n">
-        <v>56260.1878787879</v>
+        <v>56260.187878788</v>
       </c>
       <c r="F30" t="n">
         <v>0.113559176741384</v>
@@ -1387,7 +1387,7 @@
         <v>15665.3913818542</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00000230979318531673</v>
+        <v>0.00000230979318531675</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
@@ -1410,13 +1410,13 @@
         <v>1877.59393939394</v>
       </c>
       <c r="F31" t="n">
-        <v>0.068542028924247</v>
+        <v>0.0685420289242472</v>
       </c>
       <c r="G31" t="n">
         <v>1617.68181341189</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00000532142747123551</v>
+        <v>0.00000532142747123543</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
@@ -1433,19 +1433,19 @@
         <v>168.678787878788</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0000284465502597419</v>
+        <v>0.000028446550259742</v>
       </c>
       <c r="E32" t="n">
-        <v>379.721212121213</v>
+        <v>379.721212121212</v>
       </c>
       <c r="F32" t="n">
-        <v>0.15382348618658</v>
+        <v>0.153823486186581</v>
       </c>
       <c r="G32" t="n">
         <v>142.382125891489</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0000129324923719741</v>
+        <v>0.0000129324923719745</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
@@ -1462,13 +1462,13 @@
         <v>351.218181818182</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0000721687752726986</v>
+        <v>0.0000721687752726987</v>
       </c>
       <c r="E33" t="n">
         <v>985.96363636364</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0515309166222391</v>
+        <v>0.051530916622239</v>
       </c>
       <c r="G33" t="n">
         <v>246.905278986862</v>
@@ -1503,7 +1503,7 @@
         <v>54.8501941768601</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00035256224030328</v>
+        <v>0.000352562240303278</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
@@ -1520,7 +1520,7 @@
         <v>1321.61818181818</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0000340834596992882</v>
+        <v>0.0000340834596992884</v>
       </c>
       <c r="E35" t="n">
         <v>3328.2606060606</v>
@@ -1529,10 +1529,10 @@
         <v>0.0583903425682975</v>
       </c>
       <c r="G35" t="n">
-        <v>983.999962474992</v>
+        <v>983.999962474991</v>
       </c>
       <c r="H35" t="n">
-        <v>0.000000926129902654484</v>
+        <v>0.000000926129902654508</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
@@ -1549,13 +1549,13 @@
         <v>289.969696969697</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0000119776647361557</v>
+        <v>0.0000119776647361556</v>
       </c>
       <c r="E36" t="n">
         <v>303.836363636364</v>
       </c>
       <c r="F36" t="n">
-        <v>0.079514881578841</v>
+        <v>0.0795148815788409</v>
       </c>
       <c r="G36" t="n">
         <v>239.15453626661</v>
@@ -1613,10 +1613,10 @@
         <v>2819.75151515151</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0786346112206886</v>
+        <v>0.0786346112206885</v>
       </c>
       <c r="G38" t="n">
-        <v>811.009527185216</v>
+        <v>811.009527185215</v>
       </c>
       <c r="H38" t="n">
         <v>0.00000735035130525652</v>
@@ -1636,10 +1636,10 @@
         <v>79.7636363636364</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000141258770016766</v>
+        <v>0.000141258770016765</v>
       </c>
       <c r="E39" t="n">
-        <v>66.921212121212</v>
+        <v>66.9212121212119</v>
       </c>
       <c r="F39" t="n">
         <v>0.0506336360820811</v>
@@ -1648,7 +1648,7 @@
         <v>60.5278070709548</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00111190335026918</v>
+        <v>0.00111190335026916</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
@@ -1668,16 +1668,16 @@
         <v>0.000371877171466944</v>
       </c>
       <c r="E40" t="n">
-        <v>2234.26666666667</v>
+        <v>2234.26666666666</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0865195599008171</v>
+        <v>0.0865195599008187</v>
       </c>
       <c r="G40" t="n">
-        <v>762.24288519723</v>
+        <v>762.242885197232</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00000125407732414441</v>
+        <v>0.00000125407732414427</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
@@ -1694,19 +1694,19 @@
         <v>5082.62424242424</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0000387996667670895</v>
+        <v>0.0000387996667670894</v>
       </c>
       <c r="E41" t="n">
         <v>17334.6484848485</v>
       </c>
       <c r="F41" t="n">
-        <v>0.087838855026444</v>
+        <v>0.0878388550264433</v>
       </c>
       <c r="G41" t="n">
         <v>3921.75687543596</v>
       </c>
       <c r="H41" t="n">
-        <v>0.000000759716200009475</v>
+        <v>0.000000759716200009421</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
@@ -1723,19 +1723,19 @@
         <v>377.842424242424</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0000471100341754489</v>
+        <v>0.0000471100341754487</v>
       </c>
       <c r="E42" t="n">
-        <v>1113.44242424243</v>
+        <v>1113.44242424242</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0561603059704046</v>
+        <v>0.0561603059704048</v>
       </c>
       <c r="G42" t="n">
         <v>276.172303396687</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00000199123009939075</v>
+        <v>0.00000199123009939073</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
@@ -1752,19 +1752,19 @@
         <v>3652.33939393939</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0000484677132702444</v>
+        <v>0.0000484677132702445</v>
       </c>
       <c r="E43" t="n">
         <v>8519.36969696972</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0670657561664408</v>
+        <v>0.067065756166441</v>
       </c>
       <c r="G43" t="n">
         <v>2698.67982863927</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00000031909177400646</v>
+        <v>0.000000319091774006471</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
@@ -1784,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.848484848484852</v>
+        <v>-0.848484848484853</v>
       </c>
       <c r="F44" t="n">
         <v>0.762685249333531</v>
@@ -1810,19 +1810,19 @@
         <v>2213.2</v>
       </c>
       <c r="D45" t="n">
-        <v>0.000354317960502844</v>
+        <v>0.000354317960502846</v>
       </c>
       <c r="E45" t="n">
-        <v>8607.45454545455</v>
+        <v>8607.45454545459</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0599996758289117</v>
+        <v>0.0599996758289109</v>
       </c>
       <c r="G45" t="n">
-        <v>1437.74788253121</v>
+        <v>1437.7478825312</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0000467570973178666</v>
+        <v>0.0000467570973178651</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
@@ -1836,10 +1836,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>7.71515151515151</v>
+        <v>7.71515151515152</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0000898930281255927</v>
+        <v>0.000089893028125592</v>
       </c>
       <c r="E46" t="n">
         <v>-15.9515151515152</v>
@@ -1874,13 +1874,13 @@
         <v>-112.278787878787</v>
       </c>
       <c r="F47" t="n">
-        <v>0.00125302436476505</v>
+        <v>0.00125302436476504</v>
       </c>
       <c r="G47" t="n">
         <v>267.966271280733</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0000923155048268945</v>
+        <v>0.0000923155048268946</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
@@ -1926,19 +1926,19 @@
         <v>89.4484848484849</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0000969545596161511</v>
+        <v>0.0000969545596161509</v>
       </c>
       <c r="E49" t="n">
-        <v>-27.6969696969698</v>
+        <v>-27.6969696969699</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0771117420852323</v>
+        <v>0.0771117420852321</v>
       </c>
       <c r="G49" t="n">
         <v>109.202410537655</v>
       </c>
       <c r="H49" t="n">
-        <v>0.000014722032645843</v>
+        <v>0.0000147220326458428</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.53333333333334</v>
+        <v>-1.53333333333333</v>
       </c>
       <c r="F50" t="n">
         <v>0.163773021279891</v>
@@ -1984,19 +1984,19 @@
         <v>111.139393939394</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0000687148108539824</v>
+        <v>0.0000687148108539819</v>
       </c>
       <c r="E51" t="n">
-        <v>-25.3636363636365</v>
+        <v>-25.3636363636367</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0816239852512744</v>
+        <v>0.0816239852512739</v>
       </c>
       <c r="G51" t="n">
         <v>124.154888310349</v>
       </c>
       <c r="H51" t="n">
-        <v>0.000185215295097227</v>
+        <v>0.000185215295097225</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
@@ -2016,16 +2016,16 @@
         <v>0.0000165527687920154</v>
       </c>
       <c r="E52" t="n">
-        <v>-12.709090909091</v>
+        <v>-12.7090909090911</v>
       </c>
       <c r="F52" t="n">
-        <v>0.219161885417699</v>
+        <v>0.219161885417698</v>
       </c>
       <c r="G52" t="n">
         <v>41.1010786956696</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0000142452857462801</v>
+        <v>0.00001424528574628</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
@@ -2045,7 +2045,7 @@
         <v>0.000171258296776249</v>
       </c>
       <c r="E53" t="n">
-        <v>-79.1515151515151</v>
+        <v>-79.1515151515152</v>
       </c>
       <c r="F53" t="n">
         <v>0.0151867908560223</v>
@@ -2054,7 +2054,7 @@
         <v>273.793938941632</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00000446893799661168</v>
+        <v>0.00000446893799661171</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
@@ -2097,22 +2097,22 @@
         <v>21</v>
       </c>
       <c r="C55" t="n">
-        <v>314.115151515151</v>
+        <v>314.115151515152</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00000726220466635513</v>
+        <v>0.00000726220466635512</v>
       </c>
       <c r="E55" t="n">
-        <v>-491.715151515151</v>
+        <v>-491.715151515152</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0000940072701640037</v>
+        <v>0.0000940072701640064</v>
       </c>
       <c r="G55" t="n">
-        <v>497.2002640308</v>
+        <v>497.200264030799</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0000229612035322165</v>
+        <v>0.0000229612035322166</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
@@ -2129,19 +2129,19 @@
         <v>9901.10909090909</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0000675279643231019</v>
+        <v>0.0000675279643231015</v>
       </c>
       <c r="E56" t="n">
-        <v>-3087.79999999999</v>
+        <v>-3087.79999999998</v>
       </c>
       <c r="F56" t="n">
-        <v>0.028282944061957</v>
+        <v>0.0282829440619571</v>
       </c>
       <c r="G56" t="n">
         <v>13079.8993289151</v>
       </c>
       <c r="H56" t="n">
-        <v>0.000000963517836400856</v>
+        <v>0.000000963517836400849</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
@@ -2190,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>-6.42424242424242</v>
+        <v>-6.42424242424243</v>
       </c>
       <c r="F58" t="n">
         <v>0.0102836015173589</v>
@@ -2216,19 +2216,19 @@
         <v>1126.58787878788</v>
       </c>
       <c r="D59" t="n">
-        <v>0.000067449907973983</v>
+        <v>0.0000674499079739828</v>
       </c>
       <c r="E59" t="n">
-        <v>-311.927272727273</v>
+        <v>-311.927272727274</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0956660010754039</v>
+        <v>0.095666001075404</v>
       </c>
       <c r="G59" t="n">
         <v>1387.60760128994</v>
       </c>
       <c r="H59" t="n">
-        <v>0.000000296567551581968</v>
+        <v>0.000000296567551581971</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
@@ -2248,10 +2248,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0969696969696985</v>
+        <v>0.0969696969696972</v>
       </c>
       <c r="F60" t="n">
-        <v>0.894252136887354</v>
+        <v>0.894252136887355</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0.00000524526477343903</v>
       </c>
       <c r="E62" t="n">
-        <v>-62.3515151515151</v>
+        <v>-62.3515151515153</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00273151731187426</v>
+        <v>0.00273151731187432</v>
       </c>
       <c r="G62" t="n">
         <v>118.597438735602</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00000817373710091363</v>
+        <v>0.00000817373710091366</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
@@ -2332,7 +2332,7 @@
         <v>85.1272727272727</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0000779438906006061</v>
+        <v>0.0000779438906006062</v>
       </c>
       <c r="E63" t="n">
         <v>-21.4424242424243</v>
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>-9.48484848484848</v>
+        <v>-9.48484848484849</v>
       </c>
       <c r="F65" t="n">
         <v>0.0212646977120746</v>
@@ -2451,10 +2451,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.393939393939396</v>
+        <v>-0.393939393939394</v>
       </c>
       <c r="F67" t="n">
-        <v>0.81245930477778</v>
+        <v>0.812459304777781</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2480,16 +2480,16 @@
         <v>0.0257660858850149</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.94545454545455</v>
+        <v>-1.94545454545456</v>
       </c>
       <c r="F68" t="n">
-        <v>0.546144018981009</v>
+        <v>0.546144018981008</v>
       </c>
       <c r="G68" t="n">
         <v>1.96607755057206</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0372342419956883</v>
+        <v>0.0372342419956882</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
@@ -2518,7 +2518,7 @@
         <v>5.40993181881631</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0094547983646452</v>
+        <v>0.00945479836464517</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
@@ -2535,19 +2535,19 @@
         <v>58.8727272727273</v>
       </c>
       <c r="D70" t="n">
-        <v>0.000909228623390166</v>
+        <v>0.000909228623390163</v>
       </c>
       <c r="E70" t="n">
-        <v>40.3212121212121</v>
+        <v>40.3212121212123</v>
       </c>
       <c r="F70" t="n">
-        <v>0.595003063336784</v>
+        <v>0.595003063336782</v>
       </c>
       <c r="G70" t="n">
         <v>53.8871958141787</v>
       </c>
       <c r="H70" t="n">
-        <v>0.000228564257026301</v>
+        <v>0.000228564257026302</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
@@ -2564,19 +2564,19 @@
         <v>61.0969696969697</v>
       </c>
       <c r="D71" t="n">
-        <v>0.000104085818894575</v>
+        <v>0.000104085818894576</v>
       </c>
       <c r="E71" t="n">
-        <v>63.7212121212126</v>
+        <v>63.7212121212119</v>
       </c>
       <c r="F71" t="n">
-        <v>0.308282498043318</v>
+        <v>0.308282498043324</v>
       </c>
       <c r="G71" t="n">
-        <v>52.5965277142785</v>
+        <v>52.5965277142786</v>
       </c>
       <c r="H71" t="n">
-        <v>0.00000476505959682784</v>
+        <v>0.0000047650595968279</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
@@ -2593,19 +2593,19 @@
         <v>3.24848484848485</v>
       </c>
       <c r="D72" t="n">
-        <v>0.035595177263111</v>
+        <v>0.0355951772631112</v>
       </c>
       <c r="E72" t="n">
-        <v>1.3818181818182</v>
+        <v>1.38181818181822</v>
       </c>
       <c r="F72" t="n">
-        <v>0.774075792729106</v>
+        <v>0.774075792729102</v>
       </c>
       <c r="G72" t="n">
-        <v>2.96736659008472</v>
+        <v>2.96736659008471</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0158017570870926</v>
+        <v>0.0158017570870928</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
@@ -2625,10 +2625,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.484848484848495</v>
+        <v>0.484848484848484</v>
       </c>
       <c r="F73" t="n">
-        <v>0.767283534006744</v>
+        <v>0.767283534006749</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0.555240787628958</v>
       </c>
       <c r="E74" t="n">
-        <v>3.43030303030308</v>
+        <v>3.43030303030309</v>
       </c>
       <c r="F74" t="n">
-        <v>0.651483350282156</v>
+        <v>0.651483350282154</v>
       </c>
       <c r="G74" t="n">
         <v>-3.67366683178759</v>
@@ -2680,7 +2680,7 @@
         <v>-2.08484848484849</v>
       </c>
       <c r="D75" t="n">
-        <v>0.346962500741532</v>
+        <v>0.346962500741533</v>
       </c>
       <c r="E75" t="n">
         <v>-12.7515151515151</v>
@@ -2692,7 +2692,7 @@
         <v>-1.24761466164605</v>
       </c>
       <c r="H75" t="n">
-        <v>0.618058243431636</v>
+        <v>0.618058243431635</v>
       </c>
       <c r="I75" t="s">
         <v>34</v>
@@ -2738,19 +2738,19 @@
         <v>-10.7939393939394</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0150585069802605</v>
+        <v>0.0150585069802603</v>
       </c>
       <c r="E77" t="n">
         <v>18.5393939393939</v>
       </c>
       <c r="F77" t="n">
-        <v>0.382967245528646</v>
+        <v>0.382967245528645</v>
       </c>
       <c r="G77" t="n">
-        <v>-12.8955167885164</v>
+        <v>-12.8955167885165</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00352150351727314</v>
+        <v>0.00352150351727301</v>
       </c>
       <c r="I77" t="s">
         <v>37</v>
@@ -2825,16 +2825,16 @@
         <v>3.19393939393939</v>
       </c>
       <c r="D80" t="n">
-        <v>0.067948196442727</v>
+        <v>0.0679481964427272</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.45454545454545</v>
+        <v>-3.45454545454552</v>
       </c>
       <c r="F80" t="n">
-        <v>0.659665374852189</v>
+        <v>0.659665374852184</v>
       </c>
       <c r="G80" t="n">
-        <v>3.5223360075568</v>
+        <v>3.52233600755681</v>
       </c>
       <c r="H80" t="n">
         <v>0.044760109727931</v>
@@ -2854,19 +2854,19 @@
         <v>12.8727272727273</v>
       </c>
       <c r="D81" t="n">
-        <v>0.000686864060695312</v>
+        <v>0.000686864060695317</v>
       </c>
       <c r="E81" t="n">
-        <v>9.82424242424246</v>
+        <v>9.82424242424251</v>
       </c>
       <c r="F81" t="n">
-        <v>0.423554339061887</v>
+        <v>0.423554339061885</v>
       </c>
       <c r="G81" t="n">
         <v>11.4459676883519</v>
       </c>
       <c r="H81" t="n">
-        <v>0.000545218883003856</v>
+        <v>0.00054521888300387</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
@@ -2889,7 +2889,7 @@
         <v>-13.1878787878788</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0648585335698914</v>
+        <v>0.0648585335698915</v>
       </c>
       <c r="G82" t="n">
         <v>2.42188052839696</v>
@@ -2915,7 +2915,7 @@
         <v>0.105593854792505</v>
       </c>
       <c r="E83" t="n">
-        <v>0.981818181818181</v>
+        <v>0.981818181818183</v>
       </c>
       <c r="F83" t="n">
         <v>0.879045105817318</v>
@@ -2938,22 +2938,22 @@
         <v>29</v>
       </c>
       <c r="C84" t="n">
-        <v>-30.4606060606061</v>
+        <v>-30.460606060606</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0000335424492999471</v>
+        <v>0.0000335424492999469</v>
       </c>
       <c r="E84" t="n">
-        <v>45.9333333333333</v>
+        <v>45.9333333333334</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0435019500942339</v>
+        <v>0.0435019500942335</v>
       </c>
       <c r="G84" t="n">
         <v>-34.1888740385911</v>
       </c>
       <c r="H84" t="n">
-        <v>0.000157178998956358</v>
+        <v>0.000157178998956359</v>
       </c>
       <c r="I84" t="s">
         <v>37</v>
@@ -2970,19 +2970,19 @@
         <v>5.40606060606061</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0033287585958245</v>
+        <v>0.00332875859582449</v>
       </c>
       <c r="E85" t="n">
         <v>4.8969696969697</v>
       </c>
       <c r="F85" t="n">
-        <v>0.071976065924001</v>
+        <v>0.0719760659240012</v>
       </c>
       <c r="G85" t="n">
         <v>4.09074405388339</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0310549380434923</v>
+        <v>0.0310549380434922</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
@@ -3028,19 +3028,19 @@
         <v>6.2969696969697</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00535055454028802</v>
+        <v>0.005350554540288</v>
       </c>
       <c r="E87" t="n">
         <v>2.50303030303037</v>
       </c>
       <c r="F87" t="n">
-        <v>0.781296124044154</v>
+        <v>0.781296124044153</v>
       </c>
       <c r="G87" t="n">
         <v>6.03604280654753</v>
       </c>
       <c r="H87" t="n">
-        <v>0.00499129044446513</v>
+        <v>0.00499129044446511</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>35.4848484848486</v>
       </c>
       <c r="F88" t="n">
-        <v>0.00445126863099093</v>
+        <v>0.00445126863099095</v>
       </c>
       <c r="G88" t="n">
         <v>15.0909441960988</v>
@@ -3092,13 +3092,13 @@
         <v>61.8</v>
       </c>
       <c r="F89" t="n">
-        <v>0.00357324052680394</v>
+        <v>0.00357324052680395</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88770070642538</v>
+        <v>1.88770070642537</v>
       </c>
       <c r="H89" t="n">
-        <v>0.842267041681437</v>
+        <v>0.842267041681438</v>
       </c>
       <c r="I89" t="s">
         <v>11</v>
@@ -3118,16 +3118,16 @@
         <v>0.000445919185362481</v>
       </c>
       <c r="E90" t="n">
-        <v>86.1454545454545</v>
+        <v>86.1454545454547</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00834886988812452</v>
+        <v>0.00834886988812437</v>
       </c>
       <c r="G90" t="n">
         <v>23.5956958817708</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0227640635780367</v>
+        <v>0.0227640635780374</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
@@ -3144,19 +3144,19 @@
         <v>123.018181818182</v>
       </c>
       <c r="D91" t="n">
-        <v>0.000393745919362163</v>
+        <v>0.000393745919362157</v>
       </c>
       <c r="E91" t="n">
-        <v>344.242424242425</v>
+        <v>344.242424242426</v>
       </c>
       <c r="F91" t="n">
-        <v>0.000480159769015547</v>
+        <v>0.000480159769015521</v>
       </c>
       <c r="G91" t="n">
-        <v>50.234912903859</v>
+        <v>50.2349129038587</v>
       </c>
       <c r="H91" t="n">
-        <v>0.249316483150281</v>
+        <v>0.249316483150286</v>
       </c>
       <c r="I91" t="s">
         <v>11</v>
@@ -3173,19 +3173,19 @@
         <v>13.5333333333333</v>
       </c>
       <c r="D92" t="n">
-        <v>0.000208111711985663</v>
+        <v>0.000208111711985661</v>
       </c>
       <c r="E92" t="n">
         <v>15.3454545454545</v>
       </c>
       <c r="F92" t="n">
-        <v>0.128548325156535</v>
+        <v>0.128548325156536</v>
       </c>
       <c r="G92" t="n">
         <v>12.1027835167489</v>
       </c>
       <c r="H92" t="n">
-        <v>0.00154248472717273</v>
+        <v>0.00154248472717271</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
@@ -3208,10 +3208,10 @@
         <v>56.4545454545454</v>
       </c>
       <c r="F93" t="n">
-        <v>0.000374286486169155</v>
+        <v>0.000374286486169158</v>
       </c>
       <c r="G93" t="n">
-        <v>3.69345233557136</v>
+        <v>3.69345233557138</v>
       </c>
       <c r="H93" t="n">
         <v>0.83854437309631</v>
@@ -3237,13 +3237,13 @@
         <v>168.721212121212</v>
       </c>
       <c r="F94" t="n">
-        <v>0.000161566509880706</v>
+        <v>0.000161566509880707</v>
       </c>
       <c r="G94" t="n">
-        <v>24.8501830439407</v>
+        <v>24.8501830439408</v>
       </c>
       <c r="H94" t="n">
-        <v>0.61787791086047</v>
+        <v>0.617877910860467</v>
       </c>
       <c r="I94" t="s">
         <v>11</v>
@@ -3257,22 +3257,22 @@
         <v>19</v>
       </c>
       <c r="C95" t="n">
-        <v>62.3515151515152</v>
+        <v>62.3515151515151</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00539524973366033</v>
+        <v>0.00539524973366036</v>
       </c>
       <c r="E95" t="n">
         <v>130.99393939394</v>
       </c>
       <c r="F95" t="n">
-        <v>0.000306085669688194</v>
+        <v>0.000306085669688192</v>
       </c>
       <c r="G95" t="n">
-        <v>-31.2361290677373</v>
+        <v>-31.2361290677375</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0678234910832768</v>
+        <v>0.0678234910832763</v>
       </c>
       <c r="I95" t="s">
         <v>11</v>
@@ -3295,13 +3295,13 @@
         <v>1950.33333333333</v>
       </c>
       <c r="F96" t="n">
-        <v>0.00100844584896646</v>
+        <v>0.00100844584896643</v>
       </c>
       <c r="G96" t="n">
-        <v>-101.053347886917</v>
+        <v>-101.053347886919</v>
       </c>
       <c r="H96" t="n">
-        <v>0.328927295227367</v>
+        <v>0.328927295227353</v>
       </c>
       <c r="I96" t="s">
         <v>37</v>
@@ -3324,7 +3324,7 @@
         <v>747.278787878788</v>
       </c>
       <c r="F97" t="n">
-        <v>0.000690126795697782</v>
+        <v>0.00069012679569778</v>
       </c>
       <c r="G97" t="n">
         <v>137.638191523132</v>
@@ -3347,19 +3347,19 @@
         <v>117.460606060606</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00096225510935276</v>
+        <v>0.000962255109352758</v>
       </c>
       <c r="E98" t="n">
         <v>240.921212121212</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0000239929892701341</v>
+        <v>0.0000239929892701347</v>
       </c>
       <c r="G98" t="n">
-        <v>-47.7683650964322</v>
+        <v>-47.7683650964329</v>
       </c>
       <c r="H98" t="n">
-        <v>0.329998890410538</v>
+        <v>0.329998890410524</v>
       </c>
       <c r="I98" t="s">
         <v>11</v>
@@ -3379,10 +3379,10 @@
         <v>0.00117343558564654</v>
       </c>
       <c r="E99" t="n">
-        <v>-3.07878787878795</v>
+        <v>-3.07878787878792</v>
       </c>
       <c r="F99" t="n">
-        <v>0.859742250706958</v>
+        <v>0.859742250706959</v>
       </c>
       <c r="G99" t="n">
         <v>52.6575447659604</v>
@@ -3411,7 +3411,7 @@
         <v>-8.40000000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0562940910763766</v>
+        <v>0.0562940910763767</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3431,22 +3431,22 @@
         <v>25</v>
       </c>
       <c r="C101" t="n">
-        <v>36.9575757575758</v>
+        <v>36.9575757575757</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00345764590141843</v>
+        <v>0.00345764590141845</v>
       </c>
       <c r="E101" t="n">
-        <v>80.1878787878787</v>
+        <v>80.1878787878788</v>
       </c>
       <c r="F101" t="n">
-        <v>0.00128318999775187</v>
+        <v>0.00128318999775186</v>
       </c>
       <c r="G101" t="n">
-        <v>-1.96165521933528</v>
+        <v>-1.96165521933531</v>
       </c>
       <c r="H101" t="n">
-        <v>0.828023605814294</v>
+        <v>0.828023605814292</v>
       </c>
       <c r="I101" t="s">
         <v>11</v>
@@ -3492,19 +3492,19 @@
         <v>37.8606060606061</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00111436983404014</v>
+        <v>0.00111436983404013</v>
       </c>
       <c r="E103" t="n">
         <v>14.7818181818184</v>
       </c>
       <c r="F103" t="n">
-        <v>0.437562807335357</v>
+        <v>0.437562807335355</v>
       </c>
       <c r="G103" t="n">
         <v>33.2379646652165</v>
       </c>
       <c r="H103" t="n">
-        <v>0.000653062256160322</v>
+        <v>0.000653062256160325</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
@@ -3521,19 +3521,19 @@
         <v>213.212121212121</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00121028845723649</v>
+        <v>0.00121028845723648</v>
       </c>
       <c r="E104" t="n">
-        <v>437.781818181819</v>
+        <v>437.781818181817</v>
       </c>
       <c r="F104" t="n">
-        <v>0.000538114641171657</v>
+        <v>0.000538114641171691</v>
       </c>
       <c r="G104" t="n">
-        <v>5.61955566804324</v>
+        <v>5.61955566804606</v>
       </c>
       <c r="H104" t="n">
-        <v>0.918445384275307</v>
+        <v>0.918445384275266</v>
       </c>
       <c r="I104" t="s">
         <v>11</v>
@@ -3547,22 +3547,22 @@
         <v>29</v>
       </c>
       <c r="C105" t="n">
-        <v>29.969696969697</v>
+        <v>29.9696969696969</v>
       </c>
       <c r="D105" t="n">
-        <v>0.000776878865784599</v>
+        <v>0.000776878865784602</v>
       </c>
       <c r="E105" t="n">
-        <v>46.9333333333334</v>
+        <v>46.9333333333332</v>
       </c>
       <c r="F105" t="n">
-        <v>0.000788123664246384</v>
+        <v>0.000788123664246439</v>
       </c>
       <c r="G105" t="n">
-        <v>24.5925225111805</v>
+        <v>24.5925225111803</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0926957958642341</v>
+        <v>0.0926957958642327</v>
       </c>
       <c r="I105" t="s">
         <v>11</v>
@@ -3576,10 +3576,10 @@
         <v>30</v>
       </c>
       <c r="C106" t="n">
-        <v>63.3515151515151</v>
+        <v>63.3515151515152</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0023844837287558</v>
+        <v>0.00238448372875578</v>
       </c>
       <c r="E106" t="n">
         <v>37.0363636363636</v>
@@ -3588,10 +3588,10 @@
         <v>0.00256170448888988</v>
       </c>
       <c r="G106" t="n">
-        <v>22.8040971057574</v>
+        <v>22.8040971057575</v>
       </c>
       <c r="H106" t="n">
-        <v>0.324915828010093</v>
+        <v>0.324915828010092</v>
       </c>
       <c r="I106" t="s">
         <v>11</v>
@@ -3614,7 +3614,7 @@
         <v>-19.2545454545454</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0429231907021915</v>
+        <v>0.0429231907021917</v>
       </c>
       <c r="G107" t="n">
         <v>4.21990229652121</v>
@@ -3637,19 +3637,19 @@
         <v>13.9757575757576</v>
       </c>
       <c r="D108" t="n">
-        <v>0.000394570936736466</v>
+        <v>0.000394570936736465</v>
       </c>
       <c r="E108" t="n">
-        <v>41.7757575757576</v>
+        <v>41.7757575757575</v>
       </c>
       <c r="F108" t="n">
-        <v>0.000251533672577195</v>
+        <v>0.000251533672577189</v>
       </c>
       <c r="G108" t="n">
         <v>14.0349186352306</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0581727177229509</v>
+        <v>0.0581727177229516</v>
       </c>
       <c r="I108" t="s">
         <v>11</v>
@@ -3666,19 +3666,19 @@
         <v>27.4242424242424</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0000705182026263413</v>
+        <v>0.0000705182026263411</v>
       </c>
       <c r="E109" t="n">
-        <v>9.93939393939391</v>
+        <v>9.93939393939404</v>
       </c>
       <c r="F109" t="n">
-        <v>0.416552780793454</v>
+        <v>0.416552780793448</v>
       </c>
       <c r="G109" t="n">
-        <v>25.703615409865</v>
+        <v>25.7036154098649</v>
       </c>
       <c r="H109" t="n">
-        <v>0.000136830551582922</v>
+        <v>0.000136830551582924</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
@@ -3698,16 +3698,16 @@
         <v>0.000629942391277713</v>
       </c>
       <c r="E110" t="n">
-        <v>63.2</v>
+        <v>63.2000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>0.054629683548092</v>
+        <v>0.0546296835480917</v>
       </c>
       <c r="G110" t="n">
         <v>39.0775077054791</v>
       </c>
       <c r="H110" t="n">
-        <v>0.00409214081772025</v>
+        <v>0.00409214081772028</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
@@ -3721,16 +3721,16 @@
         <v>13</v>
       </c>
       <c r="C111" t="n">
-        <v>17.260606060606</v>
+        <v>17.2606060606061</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00989107786233233</v>
+        <v>0.00989107786233232</v>
       </c>
       <c r="E111" t="n">
         <v>20.8060606060607</v>
       </c>
       <c r="F111" t="n">
-        <v>0.274526025765671</v>
+        <v>0.27452602576567</v>
       </c>
       <c r="G111" t="n">
         <v>11.6627923612693</v>
@@ -3756,10 +3756,10 @@
         <v>0.0000192295508663998</v>
       </c>
       <c r="E112" t="n">
-        <v>678.484848484848</v>
+        <v>678.48484848485</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0972918501306069</v>
+        <v>0.0972918501306062</v>
       </c>
       <c r="G112" t="n">
         <v>492.281000733695</v>
@@ -3808,22 +3808,22 @@
         <v>17</v>
       </c>
       <c r="C114" t="n">
-        <v>48.4545454545455</v>
+        <v>48.4545454545454</v>
       </c>
       <c r="D114" t="n">
-        <v>0.000411191768367137</v>
+        <v>0.00041119176836714</v>
       </c>
       <c r="E114" t="n">
         <v>19.8303030303029</v>
       </c>
       <c r="F114" t="n">
-        <v>0.299114128948307</v>
+        <v>0.299114128948308</v>
       </c>
       <c r="G114" t="n">
         <v>42.0675651039208</v>
       </c>
       <c r="H114" t="n">
-        <v>0.000531300021666268</v>
+        <v>0.000531300021666269</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
@@ -3840,13 +3840,13 @@
         <v>50.0424242424242</v>
       </c>
       <c r="D115" t="n">
-        <v>0.000424726322007646</v>
+        <v>0.000424726322007645</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.272727272727211</v>
+        <v>-0.272727272727246</v>
       </c>
       <c r="F115" t="n">
-        <v>0.986712911253588</v>
+        <v>0.986712911253586</v>
       </c>
       <c r="G115" t="n">
         <v>50.1755432042238</v>
@@ -3869,19 +3869,19 @@
         <v>21.5939393939394</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0104993110502816</v>
+        <v>0.0104993110502817</v>
       </c>
       <c r="E116" t="n">
         <v>16.0060606060606</v>
       </c>
       <c r="F116" t="n">
-        <v>0.122832293432395</v>
+        <v>0.122832293432396</v>
       </c>
       <c r="G116" t="n">
         <v>13.5668418699804</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0482911212717188</v>
+        <v>0.0482911212717185</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
@@ -3898,19 +3898,19 @@
         <v>6.56363636363636</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00432612109167872</v>
+        <v>0.00432612109167873</v>
       </c>
       <c r="E117" t="n">
         <v>1.76363636363635</v>
       </c>
       <c r="F117" t="n">
-        <v>0.553425508616793</v>
+        <v>0.553425508616792</v>
       </c>
       <c r="G117" t="n">
         <v>5.86865520933574</v>
       </c>
       <c r="H117" t="n">
-        <v>0.00335403768132291</v>
+        <v>0.00335403768132293</v>
       </c>
       <c r="I117" t="s">
         <v>15</v>
@@ -3927,19 +3927,19 @@
         <v>26.4909090909091</v>
       </c>
       <c r="D118" t="n">
-        <v>0.000187615719440616</v>
+        <v>0.000187615719440617</v>
       </c>
       <c r="E118" t="n">
-        <v>7.8363636363638</v>
+        <v>7.83636363636383</v>
       </c>
       <c r="F118" t="n">
-        <v>0.474544721836581</v>
+        <v>0.474544721836579</v>
       </c>
       <c r="G118" t="n">
         <v>24.239213586554</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0000945624739562492</v>
+        <v>0.0000945624739562501</v>
       </c>
       <c r="I118" t="s">
         <v>15</v>
@@ -3953,22 +3953,22 @@
         <v>22</v>
       </c>
       <c r="C119" t="n">
-        <v>156.484848484848</v>
+        <v>156.484848484849</v>
       </c>
       <c r="D119" t="n">
-        <v>0.000551353898789217</v>
+        <v>0.000551353898789214</v>
       </c>
       <c r="E119" t="n">
-        <v>61.7878787878789</v>
+        <v>61.7878787878788</v>
       </c>
       <c r="F119" t="n">
-        <v>0.204332440008525</v>
+        <v>0.204332440008526</v>
       </c>
       <c r="G119" t="n">
-        <v>121.11978725534</v>
+        <v>121.119787255341</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0000637074699664163</v>
+        <v>0.0000637074699664159</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
@@ -3988,16 +3988,16 @@
         <v>0.002073716106019</v>
       </c>
       <c r="E120" t="n">
-        <v>1.6909090909091</v>
+        <v>1.69090909090903</v>
       </c>
       <c r="F120" t="n">
-        <v>0.820016009273209</v>
+        <v>0.820016009273215</v>
       </c>
       <c r="G120" t="n">
         <v>32.3494451653318</v>
       </c>
       <c r="H120" t="n">
-        <v>0.000687555970472083</v>
+        <v>0.000687555970472058</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
@@ -4046,16 +4046,16 @@
         <v>0.00155828483606631</v>
       </c>
       <c r="E122" t="n">
-        <v>46.2303030303029</v>
+        <v>46.2303030303031</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0428827685681644</v>
+        <v>0.042882768568163</v>
       </c>
       <c r="G122" t="n">
-        <v>20.5905060188224</v>
+        <v>20.5905060188222</v>
       </c>
       <c r="H122" t="n">
-        <v>0.00183250012361055</v>
+        <v>0.00183250012361064</v>
       </c>
       <c r="I122" t="s">
         <v>15</v>
@@ -4075,16 +4075,16 @@
         <v>0.0000539367320897942</v>
       </c>
       <c r="E123" t="n">
-        <v>317.969696969698</v>
+        <v>317.969696969699</v>
       </c>
       <c r="F123" t="n">
-        <v>0.132219697767008</v>
+        <v>0.132219697767007</v>
       </c>
       <c r="G123" t="n">
         <v>381.797521513471</v>
       </c>
       <c r="H123" t="n">
-        <v>0.000000780304414467173</v>
+        <v>0.00000078030441446717</v>
       </c>
       <c r="I123" t="s">
         <v>15</v>
@@ -4101,19 +4101,19 @@
         <v>174</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00000919116937787273</v>
+        <v>0.00000919116937787291</v>
       </c>
       <c r="E124" t="n">
         <v>108.151515151515</v>
       </c>
       <c r="F124" t="n">
-        <v>0.243876865224055</v>
+        <v>0.243876865224053</v>
       </c>
       <c r="G124" t="n">
-        <v>152.145741714718</v>
+        <v>152.145741714717</v>
       </c>
       <c r="H124" t="n">
-        <v>0.000000000475921778814373</v>
+        <v>0.000000000475921778814356</v>
       </c>
       <c r="I124" t="s">
         <v>15</v>
@@ -4130,7 +4130,7 @@
         <v>377.927272727273</v>
       </c>
       <c r="D125" t="n">
-        <v>0.00000502600179902791</v>
+        <v>0.00000502600179902789</v>
       </c>
       <c r="E125" t="n">
         <v>252.521212121211</v>
@@ -4162,7 +4162,7 @@
         <v>0.00412087497822191</v>
       </c>
       <c r="E126" t="n">
-        <v>1.87878787878788</v>
+        <v>1.87878787878789</v>
       </c>
       <c r="F126" t="n">
         <v>0.681603040967297</v>
@@ -4188,19 +4188,19 @@
         <v>42.2969696969697</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0000273595164213296</v>
+        <v>0.0000273595164213294</v>
       </c>
       <c r="E127" t="n">
-        <v>6.81818181818155</v>
+        <v>6.81818181818178</v>
       </c>
       <c r="F127" t="n">
-        <v>0.735810515380296</v>
+        <v>0.735810515380286</v>
       </c>
       <c r="G127" t="n">
-        <v>40.8695890964991</v>
+        <v>40.869589096499</v>
       </c>
       <c r="H127" t="n">
-        <v>0.00000284901777648592</v>
+        <v>0.00000284901777648599</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
@@ -4252,13 +4252,13 @@
         <v>27.1757575757577</v>
       </c>
       <c r="F129" t="n">
-        <v>0.220933655426079</v>
+        <v>0.22093365542608</v>
       </c>
       <c r="G129" t="n">
         <v>26.7607769018305</v>
       </c>
       <c r="H129" t="n">
-        <v>0.00140095100147454</v>
+        <v>0.00140095100147453</v>
       </c>
       <c r="I129" t="s">
         <v>15</v>
@@ -4368,13 +4368,13 @@
         <v>-160.072727272727</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0000299357595038515</v>
+        <v>0.0000299357595038517</v>
       </c>
       <c r="G133" t="n">
         <v>17.5366440719702</v>
       </c>
       <c r="H133" t="n">
-        <v>0.050871385083933</v>
+        <v>0.0508713850839333</v>
       </c>
       <c r="I133" t="s">
         <v>11</v>
@@ -4420,19 +4420,19 @@
         <v>-11.3333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00783963626955871</v>
+        <v>0.00783963626955873</v>
       </c>
       <c r="E135" t="n">
         <v>-197.39393939394</v>
       </c>
       <c r="F135" t="n">
-        <v>0.00250922586580973</v>
+        <v>0.00250922586580974</v>
       </c>
       <c r="G135" t="n">
-        <v>-3.57522749781081</v>
+        <v>-3.5752274978108</v>
       </c>
       <c r="H135" t="n">
-        <v>0.516154454568004</v>
+        <v>0.516154454568005</v>
       </c>
       <c r="I135" t="s">
         <v>11</v>
@@ -4507,19 +4507,19 @@
         <v>-3.06666666666667</v>
       </c>
       <c r="D138" t="n">
-        <v>0.168394337577007</v>
+        <v>0.168394337577006</v>
       </c>
       <c r="E138" t="n">
         <v>-31.0969696969697</v>
       </c>
       <c r="F138" t="n">
-        <v>0.00006179568398228</v>
+        <v>0.000061795683982281</v>
       </c>
       <c r="G138" t="n">
-        <v>6.05236646408797</v>
+        <v>6.05236646408796</v>
       </c>
       <c r="H138" t="n">
-        <v>0.267115192532719</v>
+        <v>0.267115192532718</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
@@ -4542,13 +4542,13 @@
         <v>-28.7090909090909</v>
       </c>
       <c r="F139" t="n">
-        <v>0.000422832498643565</v>
+        <v>0.000422832498643564</v>
       </c>
       <c r="G139" t="n">
-        <v>6.20036124590622</v>
+        <v>6.20036124590623</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0529758901689073</v>
+        <v>0.052975890168907</v>
       </c>
       <c r="I139" t="s">
         <v>11</v>
@@ -4565,13 +4565,13 @@
         <v>-10.5575757575758</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0358428268330848</v>
+        <v>0.0358428268330849</v>
       </c>
       <c r="E140" t="n">
         <v>-90.1696969696969</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0000910671355282929</v>
+        <v>0.0000910671355282926</v>
       </c>
       <c r="G140" t="n">
         <v>14.5072225739113</v>
@@ -4658,7 +4658,7 @@
         <v>-11.6727272727273</v>
       </c>
       <c r="F143" t="n">
-        <v>0.00179007916707476</v>
+        <v>0.00179007916707477</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.00074316939940767</v>
       </c>
       <c r="G146" t="n">
-        <v>-4.63061007763823</v>
+        <v>-4.6306100776382</v>
       </c>
       <c r="H146" t="n">
         <v>0.88137890625611</v>
@@ -4777,7 +4777,7 @@
         <v>0.00023166134618727</v>
       </c>
       <c r="G147" t="n">
-        <v>5.77435714951021</v>
+        <v>5.77435714951022</v>
       </c>
       <c r="H147" t="n">
         <v>0.264030327815714</v>
@@ -4794,7 +4794,7 @@
         <v>30</v>
       </c>
       <c r="C148" t="n">
-        <v>-77.7515151515152</v>
+        <v>-77.7515151515151</v>
       </c>
       <c r="D148" t="n">
         <v>0.00150212401064084</v>
@@ -4803,10 +4803,10 @@
         <v>-358.345454545455</v>
       </c>
       <c r="F148" t="n">
-        <v>0.000114772078019117</v>
+        <v>0.000114772078019118</v>
       </c>
       <c r="G148" t="n">
-        <v>31.8834109709158</v>
+        <v>31.8834109709157</v>
       </c>
       <c r="H148" t="n">
         <v>0.0590086967163634</v>
@@ -4852,10 +4852,10 @@
         <v>32</v>
       </c>
       <c r="C150" t="n">
-        <v>-14.0606060606061</v>
+        <v>-14.060606060606</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00511803260731293</v>
+        <v>0.00511803260731292</v>
       </c>
       <c r="E150" t="n">
         <v>-151.436363636364</v>
@@ -4864,10 +4864,10 @@
         <v>0.000178079289451002</v>
       </c>
       <c r="G150" t="n">
-        <v>8.80269738951946</v>
+        <v>8.80269738951943</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0281568495044838</v>
+        <v>0.0281568495044841</v>
       </c>
       <c r="I150" t="s">
         <v>15</v>
@@ -4884,19 +4884,19 @@
         <v>-5.15757575757576</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00628484575596536</v>
+        <v>0.00628484575596541</v>
       </c>
       <c r="E151" t="n">
-        <v>2.4969696969697</v>
+        <v>2.49696969696971</v>
       </c>
       <c r="F151" t="n">
-        <v>0.559105060682319</v>
+        <v>0.559105060682317</v>
       </c>
       <c r="G151" t="n">
         <v>-5.56779917515711</v>
       </c>
       <c r="H151" t="n">
-        <v>0.00439894676260977</v>
+        <v>0.00439894676260979</v>
       </c>
       <c r="I151" t="s">
         <v>37</v>
@@ -4910,16 +4910,16 @@
         <v>12</v>
       </c>
       <c r="C152" t="n">
-        <v>-18.0060606060606</v>
+        <v>-18.0060606060607</v>
       </c>
       <c r="D152" t="n">
         <v>0.111015616424587</v>
       </c>
       <c r="E152" t="n">
-        <v>37.90303030303</v>
+        <v>37.9030303030298</v>
       </c>
       <c r="F152" t="n">
-        <v>0.356183452380382</v>
+        <v>0.356183452380385</v>
       </c>
       <c r="G152" t="n">
         <v>-25.0202176250314</v>
@@ -4945,16 +4945,16 @@
         <v>0.024953847162134</v>
       </c>
       <c r="E153" t="n">
-        <v>25.3393939393938</v>
+        <v>25.339393939394</v>
       </c>
       <c r="F153" t="n">
-        <v>0.18527560212895</v>
+        <v>0.185275602128945</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70912886648328</v>
+        <v>9.70912886648327</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0688186472659237</v>
+        <v>0.0688186472659244</v>
       </c>
       <c r="I153" t="s">
         <v>15</v>
@@ -4968,22 +4968,22 @@
         <v>14</v>
       </c>
       <c r="C154" t="n">
-        <v>9.65454545454536</v>
+        <v>9.65454545454533</v>
       </c>
       <c r="D154" t="n">
-        <v>0.259705971728909</v>
+        <v>0.25970597172891</v>
       </c>
       <c r="E154" t="n">
         <v>132.375757575757</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0655482644860239</v>
+        <v>0.0655482644860244</v>
       </c>
       <c r="G154" t="n">
         <v>10.1340859136986</v>
       </c>
       <c r="H154" t="n">
-        <v>0.373062848015027</v>
+        <v>0.373062848015028</v>
       </c>
       <c r="I154" t="s">
         <v>34</v>
@@ -5012,7 +5012,7 @@
         <v>5.75962369466971</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0290579554932525</v>
+        <v>0.0290579554932524</v>
       </c>
       <c r="I155" t="s">
         <v>15</v>
@@ -5026,22 +5026,22 @@
         <v>17</v>
       </c>
       <c r="C156" t="n">
-        <v>5.54545454545455</v>
+        <v>5.54545454545456</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0873903265869951</v>
+        <v>0.087390326586995</v>
       </c>
       <c r="E156" t="n">
-        <v>12.1636363636364</v>
+        <v>12.1636363636363</v>
       </c>
       <c r="F156" t="n">
-        <v>0.205919931189487</v>
+        <v>0.205919931189488</v>
       </c>
       <c r="G156" t="n">
-        <v>3.82760264053794</v>
+        <v>3.82760264053795</v>
       </c>
       <c r="H156" t="n">
-        <v>0.248920067745762</v>
+        <v>0.248920067745761</v>
       </c>
       <c r="I156" t="s">
         <v>34</v>
@@ -5061,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>1.52121212121212</v>
+        <v>1.52121212121213</v>
       </c>
       <c r="F157" t="n">
-        <v>0.571064770705335</v>
+        <v>0.571064770705333</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -5093,13 +5093,13 @@
         <v>20.5030303030303</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0411014303008703</v>
+        <v>0.0411014303008705</v>
       </c>
       <c r="G158" t="n">
-        <v>0.929107353517436</v>
+        <v>0.929107353517441</v>
       </c>
       <c r="H158" t="n">
-        <v>0.769108205892469</v>
+        <v>0.769108205892468</v>
       </c>
       <c r="I158" t="s">
         <v>37</v>
@@ -5142,22 +5142,22 @@
         <v>21</v>
       </c>
       <c r="C160" t="n">
-        <v>-40.8545454545455</v>
+        <v>-40.8545454545454</v>
       </c>
       <c r="D160" t="n">
-        <v>0.000320933170864694</v>
+        <v>0.000320933170864693</v>
       </c>
       <c r="E160" t="n">
-        <v>32.5272727272727</v>
+        <v>32.5272727272728</v>
       </c>
       <c r="F160" t="n">
-        <v>0.325293115640008</v>
+        <v>0.325293115640007</v>
       </c>
       <c r="G160" t="n">
         <v>-43.1763503927723</v>
       </c>
       <c r="H160" t="n">
-        <v>0.000605815991487539</v>
+        <v>0.000605815991487536</v>
       </c>
       <c r="I160" t="s">
         <v>37</v>
@@ -5177,16 +5177,16 @@
         <v>0.0189266618911761</v>
       </c>
       <c r="E161" t="n">
-        <v>55.5939393939394</v>
+        <v>55.5939393939393</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0275555563465162</v>
+        <v>0.0275555563465164</v>
       </c>
       <c r="G161" t="n">
-        <v>7.62961927512491</v>
+        <v>7.62961927512493</v>
       </c>
       <c r="H161" t="n">
-        <v>0.339248293039494</v>
+        <v>0.339248293039493</v>
       </c>
       <c r="I161" t="s">
         <v>11</v>
@@ -5261,19 +5261,19 @@
         <v>12.4787878787879</v>
       </c>
       <c r="D164" t="n">
-        <v>0.00638550236608605</v>
+        <v>0.00638550236608604</v>
       </c>
       <c r="E164" t="n">
         <v>25.3818181818182</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0905543038847835</v>
+        <v>0.0905543038847846</v>
       </c>
       <c r="G164" t="n">
         <v>11.4234443186194</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0340698480112934</v>
+        <v>0.0340698480112931</v>
       </c>
       <c r="I164" t="s">
         <v>15</v>
@@ -5287,22 +5287,22 @@
         <v>26</v>
       </c>
       <c r="C165" t="n">
-        <v>-1.83636363636361</v>
+        <v>-1.83636363636362</v>
       </c>
       <c r="D165" t="n">
-        <v>0.642514983089579</v>
+        <v>0.642514983089577</v>
       </c>
       <c r="E165" t="n">
-        <v>5.03636363636358</v>
+        <v>5.0363636363636</v>
       </c>
       <c r="F165" t="n">
-        <v>0.741825585914345</v>
+        <v>0.741825585914344</v>
       </c>
       <c r="G165" t="n">
-        <v>-2.85661594818356</v>
+        <v>-2.85661594818357</v>
       </c>
       <c r="H165" t="n">
-        <v>0.29725038707731</v>
+        <v>0.297250387077308</v>
       </c>
       <c r="I165" t="s">
         <v>34</v>
@@ -5316,16 +5316,16 @@
         <v>27</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.715151515151516</v>
+        <v>-0.715151515151515</v>
       </c>
       <c r="D166" t="n">
         <v>0.400101629122392</v>
       </c>
       <c r="E166" t="n">
-        <v>-3.53333333333329</v>
+        <v>-3.53333333333332</v>
       </c>
       <c r="F166" t="n">
-        <v>0.54123542759969</v>
+        <v>0.541235427599688</v>
       </c>
       <c r="G166" t="n">
         <v>-0.73524274909388</v>
@@ -5351,10 +5351,10 @@
         <v>0.439200539077806</v>
       </c>
       <c r="E167" t="n">
-        <v>16.1939393939395</v>
+        <v>16.1939393939393</v>
       </c>
       <c r="F167" t="n">
-        <v>0.447233991214263</v>
+        <v>0.447233991214268</v>
       </c>
       <c r="G167" t="n">
         <v>4.22414292617449</v>
@@ -5383,13 +5383,13 @@
         <v>71.2727272727273</v>
       </c>
       <c r="F168" t="n">
-        <v>0.048196411845792</v>
+        <v>0.0481964118457917</v>
       </c>
       <c r="G168" t="n">
         <v>61.0864077399416</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0000889315485354196</v>
+        <v>0.0000889315485354204</v>
       </c>
       <c r="I168" t="s">
         <v>15</v>
@@ -5438,10 +5438,10 @@
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>0.436363636363636</v>
+        <v>0.436363636363644</v>
       </c>
       <c r="F170" t="n">
-        <v>0.795761426537873</v>
+        <v>0.795761426537868</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5470,13 +5470,13 @@
         <v>10.0969696969697</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0477856068164283</v>
+        <v>0.0477856068164277</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.0108085703228864</v>
+        <v>-0.0108085703228919</v>
       </c>
       <c r="H171" t="n">
-        <v>0.995486896404936</v>
+        <v>0.995486896404934</v>
       </c>
       <c r="I171" t="s">
         <v>37</v>
@@ -5493,19 +5493,19 @@
         <v>29.7272727272727</v>
       </c>
       <c r="D172" t="n">
-        <v>0.000763969008643291</v>
+        <v>0.000763969008643293</v>
       </c>
       <c r="E172" t="n">
         <v>11.4666666666667</v>
       </c>
       <c r="F172" t="n">
-        <v>0.180518486561616</v>
+        <v>0.180518486561618</v>
       </c>
       <c r="G172" t="n">
-        <v>23.0117464367223</v>
+        <v>23.0117464367224</v>
       </c>
       <c r="H172" t="n">
-        <v>0.000686973362841673</v>
+        <v>0.000686973362841666</v>
       </c>
       <c r="I172" t="s">
         <v>15</v>
@@ -5528,13 +5528,13 @@
         <v>47.7212121212122</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0204190574076498</v>
+        <v>0.0204190574076496</v>
       </c>
       <c r="G173" t="n">
         <v>36.6566794994858</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0365092635662008</v>
+        <v>0.0365092635662009</v>
       </c>
       <c r="I173" t="s">
         <v>15</v>
@@ -5557,13 +5557,13 @@
         <v>183.854545454545</v>
       </c>
       <c r="F174" t="n">
-        <v>0.00876369401254453</v>
+        <v>0.00876369401254444</v>
       </c>
       <c r="G174" t="n">
         <v>119.212754903211</v>
       </c>
       <c r="H174" t="n">
-        <v>0.00279866172232669</v>
+        <v>0.00279866172232677</v>
       </c>
       <c r="I174" t="s">
         <v>15</v>
@@ -5580,19 +5580,19 @@
         <v>169.090909090909</v>
       </c>
       <c r="D175" t="n">
-        <v>0.0000314383749576447</v>
+        <v>0.0000314383749576446</v>
       </c>
       <c r="E175" t="n">
         <v>200.690909090909</v>
       </c>
       <c r="F175" t="n">
-        <v>0.00102014696350296</v>
+        <v>0.00102014696350297</v>
       </c>
       <c r="G175" t="n">
-        <v>95.3198170194781</v>
+        <v>95.319817019478</v>
       </c>
       <c r="H175" t="n">
-        <v>0.0160915503237146</v>
+        <v>0.0160915503237143</v>
       </c>
       <c r="I175" t="s">
         <v>15</v>
@@ -5612,16 +5612,16 @@
         <v>0.000291617038780051</v>
       </c>
       <c r="E176" t="n">
-        <v>75.9333333333331</v>
+        <v>75.9333333333336</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0419681727643029</v>
+        <v>0.0419681727643014</v>
       </c>
       <c r="G176" t="n">
         <v>114.780374000315</v>
       </c>
       <c r="H176" t="n">
-        <v>0.00105122506527747</v>
+        <v>0.00105122506527754</v>
       </c>
       <c r="I176" t="s">
         <v>15</v>
@@ -5641,16 +5641,16 @@
         <v>0.0006175979622186</v>
       </c>
       <c r="E177" t="n">
-        <v>30.7818181818182</v>
+        <v>30.7818181818181</v>
       </c>
       <c r="F177" t="n">
-        <v>0.00171607320148791</v>
+        <v>0.00171607320148793</v>
       </c>
       <c r="G177" t="n">
-        <v>18.039197758912</v>
+        <v>18.0391977589121</v>
       </c>
       <c r="H177" t="n">
-        <v>0.185646835475325</v>
+        <v>0.185646835475322</v>
       </c>
       <c r="I177" t="s">
         <v>11</v>
@@ -5667,19 +5667,19 @@
         <v>73.4969696969697</v>
       </c>
       <c r="D178" t="n">
-        <v>0.000391599173162227</v>
+        <v>0.000391599173162228</v>
       </c>
       <c r="E178" t="n">
-        <v>40.5454545454547</v>
+        <v>40.5454545454545</v>
       </c>
       <c r="F178" t="n">
-        <v>0.00824702730316332</v>
+        <v>0.00824702730316376</v>
       </c>
       <c r="G178" t="n">
-        <v>40.1549860508683</v>
+        <v>40.1549860508686</v>
       </c>
       <c r="H178" t="n">
-        <v>0.0235971193913497</v>
+        <v>0.0235971193913481</v>
       </c>
       <c r="I178" t="s">
         <v>15</v>
@@ -5699,16 +5699,16 @@
         <v>0.000465059190161491</v>
       </c>
       <c r="E179" t="n">
-        <v>6.43030303030301</v>
+        <v>6.43030303030305</v>
       </c>
       <c r="F179" t="n">
-        <v>0.154158734776747</v>
+        <v>0.154158734776745</v>
       </c>
       <c r="G179" t="n">
         <v>11.7788682433919</v>
       </c>
       <c r="H179" t="n">
-        <v>0.00256801847373197</v>
+        <v>0.002568018473732</v>
       </c>
       <c r="I179" t="s">
         <v>15</v>
@@ -5728,10 +5728,10 @@
         <v>0.00241010454983446</v>
       </c>
       <c r="E180" t="n">
-        <v>2.58787878787876</v>
+        <v>2.58787878787877</v>
       </c>
       <c r="F180" t="n">
-        <v>0.449080187181352</v>
+        <v>0.449080187181351</v>
       </c>
       <c r="G180" t="n">
         <v>8.45173357743475</v>
@@ -5754,13 +5754,13 @@
         <v>30.5090909090909</v>
       </c>
       <c r="D181" t="n">
-        <v>0.0000778815517367441</v>
+        <v>0.000077881551736744</v>
       </c>
       <c r="E181" t="n">
         <v>22.8969696969697</v>
       </c>
       <c r="F181" t="n">
-        <v>0.00267435842348067</v>
+        <v>0.00267435842348066</v>
       </c>
       <c r="G181" t="n">
         <v>19.4147779711143</v>
@@ -5786,16 +5786,16 @@
         <v>0.000146865231119139</v>
       </c>
       <c r="E182" t="n">
-        <v>233.812121212122</v>
+        <v>233.812121212121</v>
       </c>
       <c r="F182" t="n">
-        <v>0.000235877462534127</v>
+        <v>0.000235877462534129</v>
       </c>
       <c r="G182" t="n">
-        <v>44.5303495573093</v>
+        <v>44.5303495573092</v>
       </c>
       <c r="H182" t="n">
-        <v>0.336698564417202</v>
+        <v>0.336698564417201</v>
       </c>
       <c r="I182" t="s">
         <v>11</v>
@@ -5812,19 +5812,19 @@
         <v>95</v>
       </c>
       <c r="D183" t="n">
-        <v>0.000952465323142064</v>
+        <v>0.000952465323142063</v>
       </c>
       <c r="E183" t="n">
         <v>26.5878787878788</v>
       </c>
       <c r="F183" t="n">
-        <v>0.194121432646906</v>
+        <v>0.194121432646907</v>
       </c>
       <c r="G183" t="n">
-        <v>72.3346159031235</v>
+        <v>72.3346159031236</v>
       </c>
       <c r="H183" t="n">
-        <v>0.00042755607775601</v>
+        <v>0.000427556077756006</v>
       </c>
       <c r="I183" t="s">
         <v>15</v>
@@ -5838,16 +5838,16 @@
         <v>24</v>
       </c>
       <c r="C184" t="n">
-        <v>8.48484848484848</v>
+        <v>8.48484848484849</v>
       </c>
       <c r="D184" t="n">
-        <v>0.000312330199712104</v>
+        <v>0.000312330199712103</v>
       </c>
       <c r="E184" t="n">
-        <v>-9.49696969696973</v>
+        <v>-9.49696969696972</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0615559678993457</v>
+        <v>0.0615559678993458</v>
       </c>
       <c r="G184" t="n">
         <v>10.8541748774866</v>
@@ -5876,13 +5876,13 @@
         <v>38.6121212121212</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0404791959791737</v>
+        <v>0.0404791959791734</v>
       </c>
       <c r="G185" t="n">
-        <v>52.793868425655</v>
+        <v>52.7938684256549</v>
       </c>
       <c r="H185" t="n">
-        <v>0.00382779037368872</v>
+        <v>0.00382779037368876</v>
       </c>
       <c r="I185" t="s">
         <v>15</v>
@@ -5899,19 +5899,19 @@
         <v>264.339393939394</v>
       </c>
       <c r="D186" t="n">
-        <v>0.0000919885159164472</v>
+        <v>0.000091988515916447</v>
       </c>
       <c r="E186" t="n">
         <v>174.381818181818</v>
       </c>
       <c r="F186" t="n">
-        <v>0.00582937997589392</v>
+        <v>0.00582937997589388</v>
       </c>
       <c r="G186" t="n">
         <v>139.66677727997</v>
       </c>
       <c r="H186" t="n">
-        <v>0.00117627239283448</v>
+        <v>0.00117627239283451</v>
       </c>
       <c r="I186" t="s">
         <v>15</v>
@@ -5940,7 +5940,7 @@
         <v>53.5829418088543</v>
       </c>
       <c r="H187" t="n">
-        <v>0.000430061327089587</v>
+        <v>0.000430061327089586</v>
       </c>
       <c r="I187" t="s">
         <v>15</v>
@@ -5957,16 +5957,16 @@
         <v>152.981818181818</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00020664996269419</v>
+        <v>0.000206649962694188</v>
       </c>
       <c r="E188" t="n">
         <v>108.975757575757</v>
       </c>
       <c r="F188" t="n">
-        <v>0.00715071264629134</v>
+        <v>0.00715071264629133</v>
       </c>
       <c r="G188" t="n">
-        <v>83.5980713946333</v>
+        <v>83.5980713946334</v>
       </c>
       <c r="H188" t="n">
         <v>0.0103528132284091</v>
@@ -5992,13 +5992,13 @@
         <v>26.4303030303031</v>
       </c>
       <c r="F189" t="n">
-        <v>0.179716693335499</v>
+        <v>0.1797166933355</v>
       </c>
       <c r="G189" t="n">
         <v>50.9606391310099</v>
       </c>
       <c r="H189" t="n">
-        <v>0.0000524071651938583</v>
+        <v>0.0000524071651938582</v>
       </c>
       <c r="I189" t="s">
         <v>15</v>
@@ -6021,13 +6021,13 @@
         <v>15.9272727272727</v>
       </c>
       <c r="F190" t="n">
-        <v>0.00479083356023021</v>
+        <v>0.00479083356023022</v>
       </c>
       <c r="G190" t="n">
         <v>8.71030883180543</v>
       </c>
       <c r="H190" t="n">
-        <v>0.0337313285338122</v>
+        <v>0.0337313285338121</v>
       </c>
       <c r="I190" t="s">
         <v>15</v>
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>-3.72121212121213</v>
+        <v>-3.72121212121212</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0667440016824584</v>
+        <v>0.0667440016824585</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -6073,19 +6073,19 @@
         <v>65.5818181818182</v>
       </c>
       <c r="D192" t="n">
-        <v>0.000766699705871423</v>
+        <v>0.000766699705871425</v>
       </c>
       <c r="E192" t="n">
         <v>52.9454545454547</v>
       </c>
       <c r="F192" t="n">
-        <v>0.00459430140298557</v>
+        <v>0.00459430140298552</v>
       </c>
       <c r="G192" t="n">
-        <v>23.9037464587925</v>
+        <v>23.9037464587924</v>
       </c>
       <c r="H192" t="n">
-        <v>0.0790085453438872</v>
+        <v>0.0790085453438887</v>
       </c>
       <c r="I192" t="s">
         <v>11</v>
@@ -6108,7 +6108,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="F193" t="n">
-        <v>0.81437033270002</v>
+        <v>0.814370332700021</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -6131,19 +6131,19 @@
         <v>-4.98181818181818</v>
       </c>
       <c r="D194" t="n">
-        <v>0.000132273465503118</v>
+        <v>0.000132273465503119</v>
       </c>
       <c r="E194" t="n">
         <v>-9.17575757575759</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0925437716952201</v>
+        <v>0.0925437716952203</v>
       </c>
       <c r="G194" t="n">
         <v>-5.38769589932271</v>
       </c>
       <c r="H194" t="n">
-        <v>0.000544535324191536</v>
+        <v>0.000544535324191538</v>
       </c>
       <c r="I194" t="s">
         <v>37</v>
@@ -6186,7 +6186,7 @@
         <v>14</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0727272727272732</v>
+        <v>0.0727272727272724</v>
       </c>
       <c r="D196" t="n">
         <v>0.955726702681672</v>
@@ -6259,7 +6259,7 @@
         <v>4.91609229886256</v>
       </c>
       <c r="H198" t="n">
-        <v>0.236120356553718</v>
+        <v>0.236120356553719</v>
       </c>
       <c r="I198" t="s">
         <v>34</v>
@@ -6279,10 +6279,10 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>2.24242424242425</v>
+        <v>2.24242424242424</v>
       </c>
       <c r="F199" t="n">
-        <v>0.179472841509571</v>
+        <v>0.179472841509572</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6395,10 +6395,10 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.618181818181822</v>
+        <v>-0.618181818181824</v>
       </c>
       <c r="F203" t="n">
-        <v>0.610615105862108</v>
+        <v>0.610615105862107</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6569,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>2.24848484848486</v>
+        <v>2.24848484848484</v>
       </c>
       <c r="F209" t="n">
-        <v>0.108842179266201</v>
+        <v>0.108842179266203</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6598,10 +6598,10 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0.618181818181827</v>
+        <v>0.61818181818182</v>
       </c>
       <c r="F210" t="n">
-        <v>0.77315306849669</v>
+        <v>0.773153068496693</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>-1.85454545454546</v>
+        <v>-1.85454545454545</v>
       </c>
       <c r="F211" t="n">
         <v>0.120572947641175</v>
@@ -7091,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0.375757575757575</v>
+        <v>0.375757575757576</v>
       </c>
       <c r="F227" t="n">
         <v>0.776104396915175</v>
@@ -7146,19 +7146,19 @@
         <v>8.61818181818181</v>
       </c>
       <c r="D229" t="n">
-        <v>0.0175021114857284</v>
+        <v>0.0175021114857285</v>
       </c>
       <c r="E229" t="n">
         <v>29.5999999999999</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0564464293961567</v>
+        <v>0.056446429396157</v>
       </c>
       <c r="G229" t="n">
         <v>12.2078751742295</v>
       </c>
       <c r="H229" t="n">
-        <v>0.00724892083986841</v>
+        <v>0.00724892083986839</v>
       </c>
       <c r="I229" t="s">
         <v>15</v>
@@ -7381,10 +7381,10 @@
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>-8.39393939393939</v>
+        <v>-8.3939393939394</v>
       </c>
       <c r="F237" t="n">
-        <v>0.000795259333609014</v>
+        <v>0.000795259333609013</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7787,13 +7787,13 @@
         <v>0.312438392591576</v>
       </c>
       <c r="E251" t="n">
-        <v>-85.0181818181819</v>
+        <v>-85.0181818181818</v>
       </c>
       <c r="F251" t="n">
         <v>0.000224523410906164</v>
       </c>
       <c r="G251" t="n">
-        <v>7.15670149137659</v>
+        <v>7.15670149137658</v>
       </c>
       <c r="H251" t="n">
         <v>0.0634621470793585</v>
@@ -7877,7 +7877,7 @@
         <v>-9.13939393939395</v>
       </c>
       <c r="F254" t="n">
-        <v>0.00501895263693953</v>
+        <v>0.00501895263693954</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>39.6242424242424</v>
       </c>
       <c r="D258" t="n">
-        <v>0.0000755870178474952</v>
+        <v>0.0000755870178474951</v>
       </c>
       <c r="E258" t="n">
         <v>34.8121212121211</v>
@@ -7999,7 +7999,7 @@
         <v>29.881254937422</v>
       </c>
       <c r="H258" t="n">
-        <v>0.0192512476602205</v>
+        <v>0.0192512476602204</v>
       </c>
       <c r="I258" t="s">
         <v>15</v>
@@ -8109,13 +8109,13 @@
         <v>14</v>
       </c>
       <c r="F262" t="n">
-        <v>0.00220367708144136</v>
+        <v>0.00220367708144133</v>
       </c>
       <c r="G262" t="n">
-        <v>10.8240285983011</v>
+        <v>10.8240285983012</v>
       </c>
       <c r="H262" t="n">
-        <v>0.0416176522803573</v>
+        <v>0.0416176522803576</v>
       </c>
       <c r="I262" t="s">
         <v>15</v>
@@ -8248,13 +8248,13 @@
         <v>10.4242424242424</v>
       </c>
       <c r="D267" t="n">
-        <v>0.00550514578863443</v>
+        <v>0.00550514578863442</v>
       </c>
       <c r="E267" t="n">
-        <v>6.92121212121212</v>
+        <v>6.92121212121211</v>
       </c>
       <c r="F267" t="n">
-        <v>0.0858166561977803</v>
+        <v>0.0858166561977806</v>
       </c>
       <c r="G267" t="n">
         <v>9.65924780707238</v>
@@ -8422,19 +8422,19 @@
         <v>2014.98181818182</v>
       </c>
       <c r="D273" t="n">
-        <v>0.000024366549781905</v>
+        <v>0.0000243665497819049</v>
       </c>
       <c r="E273" t="n">
-        <v>2379.35757575758</v>
+        <v>2379.35757575757</v>
       </c>
       <c r="F273" t="n">
-        <v>0.000123013011737651</v>
+        <v>0.000123013011737652</v>
       </c>
       <c r="G273" t="n">
-        <v>647.898321817583</v>
+        <v>647.898321817582</v>
       </c>
       <c r="H273" t="n">
-        <v>0.102082588235873</v>
+        <v>0.102082588235871</v>
       </c>
       <c r="I273" t="s">
         <v>11</v>
@@ -8544,7 +8544,7 @@
         <v>-1.06060606060606</v>
       </c>
       <c r="F277" t="n">
-        <v>0.429455474236896</v>
+        <v>0.429455474236897</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
         <v>-3.97575757575758</v>
       </c>
       <c r="F280" t="n">
-        <v>0.00609139179403245</v>
+        <v>0.00609139179403247</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8689,13 +8689,13 @@
         <v>-711.145454545456</v>
       </c>
       <c r="F282" t="n">
-        <v>0.00165652796181437</v>
+        <v>0.00165652796181436</v>
       </c>
       <c r="G282" t="n">
         <v>1660.77535573353</v>
       </c>
       <c r="H282" t="n">
-        <v>0.0000314238368735156</v>
+        <v>0.0000314238368735158</v>
       </c>
       <c r="I282" t="s">
         <v>15</v>
@@ -8712,19 +8712,19 @@
         <v>83.8969696969697</v>
       </c>
       <c r="D283" t="n">
-        <v>0.00000355651998751434</v>
+        <v>0.00000355651998751435</v>
       </c>
       <c r="E283" t="n">
         <v>-58.3515151515153</v>
       </c>
       <c r="F283" t="n">
-        <v>0.000183758374395314</v>
+        <v>0.000183758374395316</v>
       </c>
       <c r="G283" t="n">
-        <v>104.878050350817</v>
+        <v>104.878050350816</v>
       </c>
       <c r="H283" t="n">
-        <v>0.000672791602094363</v>
+        <v>0.000672791602094358</v>
       </c>
       <c r="I283" t="s">
         <v>15</v>
@@ -8915,19 +8915,19 @@
         <v>32.2484848484848</v>
       </c>
       <c r="D290" t="n">
-        <v>0.000000287113125351879</v>
+        <v>0.00000028711312535188</v>
       </c>
       <c r="E290" t="n">
-        <v>-19.2121212121212</v>
+        <v>-19.2121212121213</v>
       </c>
       <c r="F290" t="n">
-        <v>0.0614494767111229</v>
+        <v>0.0614494767111225</v>
       </c>
       <c r="G290" t="n">
         <v>33.6629743946176</v>
       </c>
       <c r="H290" t="n">
-        <v>0.00000432886944631676</v>
+        <v>0.00000432886944631673</v>
       </c>
       <c r="I290" t="s">
         <v>15</v>
@@ -8979,7 +8979,7 @@
         <v>-2.6969696969697</v>
       </c>
       <c r="F292" t="n">
-        <v>0.000749341475898448</v>
+        <v>0.000749341475898449</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -9008,7 +9008,7 @@
         <v>-6.51515151515152</v>
       </c>
       <c r="F293" t="n">
-        <v>0.00682563881980443</v>
+        <v>0.00682563881980444</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
         <v>0.00000161358973658668</v>
       </c>
       <c r="E295" t="n">
-        <v>-19.1454545454545</v>
+        <v>-19.1454545454546</v>
       </c>
       <c r="F295" t="n">
         <v>0.101741763354327</v>
@@ -9089,10 +9089,10 @@
         <v>6.38181818181818</v>
       </c>
       <c r="D296" t="n">
-        <v>0.00000798869638982415</v>
+        <v>0.00000798869638982417</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.127272727272718</v>
+        <v>-0.127272727272719</v>
       </c>
       <c r="F296" t="n">
         <v>0.958239245333738</v>
@@ -9179,16 +9179,16 @@
         <v>0.0000249411996367195</v>
       </c>
       <c r="E299" t="n">
-        <v>1.76969696969699</v>
+        <v>1.76969696969698</v>
       </c>
       <c r="F299" t="n">
-        <v>0.471880114373243</v>
+        <v>0.471880114373247</v>
       </c>
       <c r="G299" t="n">
         <v>10.0075427799711</v>
       </c>
       <c r="H299" t="n">
-        <v>0.000108188213591016</v>
+        <v>0.000108188213591015</v>
       </c>
       <c r="I299" t="s">
         <v>15</v>
@@ -9208,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="E300" t="n">
-        <v>5.50303030303031</v>
+        <v>5.5030303030303</v>
       </c>
       <c r="F300" t="n">
         <v>0.00150255713420254</v>
@@ -9237,10 +9237,10 @@
         <v>1</v>
       </c>
       <c r="E301" t="n">
-        <v>0.175757575757573</v>
+        <v>0.175757575757566</v>
       </c>
       <c r="F301" t="n">
-        <v>0.925446068706437</v>
+        <v>0.92544606870644</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
@@ -9266,10 +9266,10 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>-0.545454545454545</v>
+        <v>-0.545454545454546</v>
       </c>
       <c r="F302" t="n">
-        <v>0.477140171963983</v>
+        <v>0.477140171963981</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -9498,10 +9498,10 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>-0.266666666666667</v>
+        <v>-0.266666666666665</v>
       </c>
       <c r="F310" t="n">
-        <v>0.641178568829546</v>
+        <v>0.641178568829548</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>-0.0424242424242426</v>
+        <v>-0.0424242424242429</v>
       </c>
       <c r="F312" t="n">
         <v>0.952671304847098</v>
@@ -10400,7 +10400,7 @@
         <v>3.88484848484849</v>
       </c>
       <c r="F341" t="n">
-        <v>0.0000691747539423139</v>
+        <v>0.0000691747539423142</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
@@ -10455,10 +10455,10 @@
         <v>0.0168005887799766</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.393939393939406</v>
+        <v>-0.39393939393941</v>
       </c>
       <c r="F343" t="n">
-        <v>0.850758508150026</v>
+        <v>0.850758508150025</v>
       </c>
       <c r="G343" t="n">
         <v>-3.04096975168493</v>
@@ -10742,13 +10742,13 @@
         <v>-48.3333333333333</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0000000617698714602395</v>
+        <v>0.0000000617698714602394</v>
       </c>
       <c r="E353" t="n">
         <v>23.4787878787879</v>
       </c>
       <c r="F353" t="n">
-        <v>0.0665592902821307</v>
+        <v>0.0665592902821309</v>
       </c>
       <c r="G353" t="n">
         <v>-51.7178270672189</v>
@@ -11015,7 +11015,7 @@
         <v>19.9754650494234</v>
       </c>
       <c r="H362" t="n">
-        <v>0.050812187707231</v>
+        <v>0.0508121877072309</v>
       </c>
       <c r="I362" t="s">
         <v>11</v>
@@ -11119,7 +11119,7 @@
         <v>264.418181818182</v>
       </c>
       <c r="D366" t="n">
-        <v>0.00000551829403191672</v>
+        <v>0.00000551829403191677</v>
       </c>
       <c r="E366" t="n">
         <v>580.606060606061</v>
@@ -11131,7 +11131,7 @@
         <v>108.289018342369</v>
       </c>
       <c r="H366" t="n">
-        <v>0.238584189185619</v>
+        <v>0.23858418918562</v>
       </c>
       <c r="I366" t="s">
         <v>11</v>
@@ -11177,13 +11177,13 @@
         <v>17.0909090909091</v>
       </c>
       <c r="D368" t="n">
-        <v>0.0000467212243507734</v>
+        <v>0.0000467212243507732</v>
       </c>
       <c r="E368" t="n">
         <v>26.2181818181818</v>
       </c>
       <c r="F368" t="n">
-        <v>0.00238311954171426</v>
+        <v>0.00238311954171424</v>
       </c>
       <c r="G368" t="n">
         <v>12.0936944959575</v>
@@ -11354,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>8.0909090909091</v>
+        <v>8.09090909090909</v>
       </c>
       <c r="F374" t="n">
         <v>0.00142527636288112</v>
@@ -11583,19 +11583,19 @@
         <v>38.0545454545455</v>
       </c>
       <c r="D382" t="n">
-        <v>0.000115260972348209</v>
+        <v>0.00011526097234821</v>
       </c>
       <c r="E382" t="n">
-        <v>-1.16363636363633</v>
+        <v>-1.16363636363608</v>
       </c>
       <c r="F382" t="n">
-        <v>0.955486272393283</v>
+        <v>0.955486272393292</v>
       </c>
       <c r="G382" t="n">
-        <v>38.2574356006586</v>
+        <v>38.2574356006585</v>
       </c>
       <c r="H382" t="n">
-        <v>0.000057599779985836</v>
+        <v>0.0000575997799858358</v>
       </c>
       <c r="I382" t="s">
         <v>15</v>
@@ -11612,13 +11612,13 @@
         <v>64.4424242424242</v>
       </c>
       <c r="D383" t="n">
-        <v>0.000088527532128103</v>
+        <v>0.0000885275321281029</v>
       </c>
       <c r="E383" t="n">
-        <v>8.68484848484835</v>
+        <v>8.68484848484842</v>
       </c>
       <c r="F383" t="n">
-        <v>0.751455342530844</v>
+        <v>0.751455342530842</v>
       </c>
       <c r="G383" t="n">
         <v>62.5761610927601</v>
@@ -11670,13 +11670,13 @@
         <v>226.369696969697</v>
       </c>
       <c r="D385" t="n">
-        <v>0.000665583237350889</v>
+        <v>0.00066558323735089</v>
       </c>
       <c r="E385" t="n">
-        <v>-9.7212121212119</v>
+        <v>-9.72121212121223</v>
       </c>
       <c r="F385" t="n">
-        <v>0.947368101069396</v>
+        <v>0.947368101069394</v>
       </c>
       <c r="G385" t="n">
         <v>228.449826761524</v>
@@ -11699,19 +11699,19 @@
         <v>60.3939393939394</v>
       </c>
       <c r="D386" t="n">
-        <v>0.0000566283017076416</v>
+        <v>0.0000566283017076417</v>
       </c>
       <c r="E386" t="n">
         <v>1.0363636363635</v>
       </c>
       <c r="F386" t="n">
-        <v>0.96326934126296</v>
+        <v>0.963269341262959</v>
       </c>
       <c r="G386" t="n">
         <v>60.1912734564214</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0000582753642574457</v>
+        <v>0.0000582753642574458</v>
       </c>
       <c r="I386" t="s">
         <v>15</v>
@@ -11731,16 +11731,16 @@
         <v>0.0000320889395528661</v>
       </c>
       <c r="E387" t="n">
-        <v>66.2484848484852</v>
+        <v>66.2484848484855</v>
       </c>
       <c r="F387" t="n">
-        <v>0.126153604295052</v>
+        <v>0.126153604295049</v>
       </c>
       <c r="G387" t="n">
         <v>151.780439019221</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0000593676448066003</v>
+        <v>0.000059367644806601</v>
       </c>
       <c r="I387" t="s">
         <v>15</v>
@@ -11760,16 +11760,16 @@
         <v>0.00102815690853782</v>
       </c>
       <c r="E388" t="n">
-        <v>-13.387878787879</v>
+        <v>-13.3878787878791</v>
       </c>
       <c r="F388" t="n">
-        <v>0.53826017690084</v>
+        <v>0.538260176900839</v>
       </c>
       <c r="G388" t="n">
         <v>65.1966481809838</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0000765949476952207</v>
+        <v>0.000076594947695221</v>
       </c>
       <c r="I388" t="s">
         <v>15</v>
@@ -11786,19 +11786,19 @@
         <v>22.2545454545455</v>
       </c>
       <c r="D389" t="n">
-        <v>0.0000135713921868285</v>
+        <v>0.0000135713921868284</v>
       </c>
       <c r="E389" t="n">
-        <v>-9.95757575757567</v>
+        <v>-9.95757575757575</v>
       </c>
       <c r="F389" t="n">
-        <v>0.448572772672829</v>
+        <v>0.448572772672827</v>
       </c>
       <c r="G389" t="n">
         <v>23.7129621700835</v>
       </c>
       <c r="H389" t="n">
-        <v>0.00000206539023189122</v>
+        <v>0.00000206539023189124</v>
       </c>
       <c r="I389" t="s">
         <v>15</v>
@@ -11815,19 +11815,19 @@
         <v>21.0060606060606</v>
       </c>
       <c r="D390" t="n">
-        <v>0.000364610764882845</v>
+        <v>0.000364610764882843</v>
       </c>
       <c r="E390" t="n">
-        <v>-11.1030303030303</v>
+        <v>-11.1030303030302</v>
       </c>
       <c r="F390" t="n">
-        <v>0.523014796996782</v>
+        <v>0.523014796996785</v>
       </c>
       <c r="G390" t="n">
         <v>22.3019543735195</v>
       </c>
       <c r="H390" t="n">
-        <v>0.000255533904419576</v>
+        <v>0.000255533904419575</v>
       </c>
       <c r="I390" t="s">
         <v>15</v>
@@ -11847,16 +11847,16 @@
         <v>0.00116275987928418</v>
       </c>
       <c r="E391" t="n">
-        <v>-1.97575757575759</v>
+        <v>-1.97575757575758</v>
       </c>
       <c r="F391" t="n">
-        <v>0.723712762894144</v>
+        <v>0.723712762894145</v>
       </c>
       <c r="G391" t="n">
         <v>15.0054579787372</v>
       </c>
       <c r="H391" t="n">
-        <v>0.000411021539008838</v>
+        <v>0.000411021539008837</v>
       </c>
       <c r="I391" t="s">
         <v>15</v>
@@ -11873,19 +11873,19 @@
         <v>134.836363636364</v>
       </c>
       <c r="D392" t="n">
-        <v>0.000373609238000923</v>
+        <v>0.000373609238000924</v>
       </c>
       <c r="E392" t="n">
-        <v>-19.187878787879</v>
+        <v>-19.1878787878788</v>
       </c>
       <c r="F392" t="n">
-        <v>0.717557153271073</v>
+        <v>0.717557153271076</v>
       </c>
       <c r="G392" t="n">
         <v>142.314343413657</v>
       </c>
       <c r="H392" t="n">
-        <v>0.00000795069667317353</v>
+        <v>0.00000795069667317339</v>
       </c>
       <c r="I392" t="s">
         <v>15</v>
@@ -11902,19 +11902,19 @@
         <v>14.630303030303</v>
       </c>
       <c r="D393" t="n">
-        <v>0.00035917355180109</v>
+        <v>0.000359173551801089</v>
       </c>
       <c r="E393" t="n">
-        <v>6.54545454545457</v>
+        <v>6.54545454545451</v>
       </c>
       <c r="F393" t="n">
-        <v>0.324484073502346</v>
+        <v>0.324484073502351</v>
       </c>
       <c r="G393" t="n">
-        <v>12.5591823525882</v>
+        <v>12.5591823525883</v>
       </c>
       <c r="H393" t="n">
-        <v>0.000155527066505813</v>
+        <v>0.000155527066505806</v>
       </c>
       <c r="I393" t="s">
         <v>15</v>
@@ -11934,10 +11934,10 @@
         <v>1</v>
       </c>
       <c r="E394" t="n">
-        <v>0.763636363636366</v>
+        <v>0.763636363636365</v>
       </c>
       <c r="F394" t="n">
-        <v>0.661272504556724</v>
+        <v>0.661272504556725</v>
       </c>
       <c r="G394" t="n">
         <v>0</v>
@@ -11960,19 +11960,19 @@
         <v>108.448484848485</v>
       </c>
       <c r="D395" t="n">
-        <v>0.000506863201586793</v>
+        <v>0.000506863201586795</v>
       </c>
       <c r="E395" t="n">
         <v>-90.0303030303028</v>
       </c>
       <c r="F395" t="n">
-        <v>0.244378147168658</v>
+        <v>0.244378147168659</v>
       </c>
       <c r="G395" t="n">
         <v>128.409687723334</v>
       </c>
       <c r="H395" t="n">
-        <v>0.0000222248747061349</v>
+        <v>0.0000222248747061348</v>
       </c>
       <c r="I395" t="s">
         <v>15</v>
@@ -11989,10 +11989,10 @@
         <v>66.1272727272727</v>
       </c>
       <c r="D396" t="n">
-        <v>0.000072289294220992</v>
+        <v>0.0000722892942209923</v>
       </c>
       <c r="E396" t="n">
-        <v>-43.1454545454545</v>
+        <v>-43.1454545454546</v>
       </c>
       <c r="F396" t="n">
         <v>0.279122653490333</v>
@@ -12001,7 +12001,7 @@
         <v>75.0043949377475</v>
       </c>
       <c r="H396" t="n">
-        <v>0.00000182273509203419</v>
+        <v>0.00000182273509203421</v>
       </c>
       <c r="I396" t="s">
         <v>15</v>
@@ -12018,10 +12018,10 @@
         <v>28.3151515151515</v>
       </c>
       <c r="D397" t="n">
-        <v>0.0000091569200557936</v>
+        <v>0.00000915692005579345</v>
       </c>
       <c r="E397" t="n">
-        <v>-5.91515151515135</v>
+        <v>-5.91515151515134</v>
       </c>
       <c r="F397" t="n">
         <v>0.508442152430639</v>
@@ -12030,7 +12030,7 @@
         <v>29.0000231834264</v>
       </c>
       <c r="H397" t="n">
-        <v>0.0000241470762132394</v>
+        <v>0.0000241470762132391</v>
       </c>
       <c r="I397" t="s">
         <v>15</v>
@@ -12047,7 +12047,7 @@
         <v>139.975757575758</v>
       </c>
       <c r="D398" t="n">
-        <v>0.0000133725459068882</v>
+        <v>0.0000133725459068881</v>
       </c>
       <c r="E398" t="n">
         <v>-18.3575757575759</v>
@@ -12059,7 +12059,7 @@
         <v>142.384388905765</v>
       </c>
       <c r="H398" t="n">
-        <v>0.0000167050849187515</v>
+        <v>0.0000167050849187516</v>
       </c>
       <c r="I398" t="s">
         <v>15</v>
@@ -12076,19 +12076,19 @@
         <v>158.012121212121</v>
       </c>
       <c r="D399" t="n">
-        <v>0.000031646141887747</v>
+        <v>0.0000316461418877467</v>
       </c>
       <c r="E399" t="n">
-        <v>-80.1333333333341</v>
+        <v>-80.1333333333343</v>
       </c>
       <c r="F399" t="n">
-        <v>0.35288821905884</v>
+        <v>0.352888219058839</v>
       </c>
       <c r="G399" t="n">
         <v>169.872711234793</v>
       </c>
       <c r="H399" t="n">
-        <v>0.0000176152211908544</v>
+        <v>0.0000176152211908545</v>
       </c>
       <c r="I399" t="s">
         <v>15</v>
@@ -12108,10 +12108,10 @@
         <v>0.00109081933636615</v>
       </c>
       <c r="E400" t="n">
-        <v>2.78181818181823</v>
+        <v>2.7818181818182</v>
       </c>
       <c r="F400" t="n">
-        <v>0.653259936516946</v>
+        <v>0.65325993651695</v>
       </c>
       <c r="G400" t="n">
         <v>11.8513965883044</v>
@@ -12137,10 +12137,10 @@
         <v>0.0118491813098001</v>
       </c>
       <c r="E401" t="n">
-        <v>-2.69696969696972</v>
+        <v>-2.69696969696973</v>
       </c>
       <c r="F401" t="n">
-        <v>0.620346604113875</v>
+        <v>0.620346604113873</v>
       </c>
       <c r="G401" t="n">
         <v>6.20811792538184</v>
@@ -12163,7 +12163,7 @@
         <v>21.2545454545455</v>
       </c>
       <c r="D402" t="n">
-        <v>0.000291635949503014</v>
+        <v>0.000291635949503015</v>
       </c>
       <c r="E402" t="n">
         <v>-16.8060606060606</v>
@@ -12198,7 +12198,7 @@
         <v>1.15151515151515</v>
       </c>
       <c r="F403" t="n">
-        <v>0.476803412337815</v>
+        <v>0.476803412337816</v>
       </c>
       <c r="G403" t="n">
         <v>0</v>
@@ -12314,7 +12314,7 @@
         <v>1.06060606060606</v>
       </c>
       <c r="F407" t="n">
-        <v>0.446068530019307</v>
+        <v>0.446068530019306</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
@@ -12337,19 +12337,19 @@
         <v>8.59393939393939</v>
       </c>
       <c r="D408" t="n">
-        <v>0.00123479838696181</v>
+        <v>0.0012347983869618</v>
       </c>
       <c r="E408" t="n">
-        <v>-0.157575757575764</v>
+        <v>-0.157575757575775</v>
       </c>
       <c r="F408" t="n">
-        <v>0.966545878773527</v>
+        <v>0.966545878773524</v>
       </c>
       <c r="G408" t="n">
         <v>8.61955020919054</v>
       </c>
       <c r="H408" t="n">
-        <v>0.00184971891278408</v>
+        <v>0.00184971891278407</v>
       </c>
       <c r="I408" t="s">
         <v>15</v>
@@ -12398,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="E410" t="n">
-        <v>0.460606060606054</v>
+        <v>0.460606060606053</v>
       </c>
       <c r="F410" t="n">
         <v>0.740009587163594</v>
@@ -12424,13 +12424,13 @@
         <v>17.7515151515152</v>
       </c>
       <c r="D411" t="n">
-        <v>0.0000928653271044284</v>
+        <v>0.0000928653271044289</v>
       </c>
       <c r="E411" t="n">
-        <v>-4.55151515151511</v>
+        <v>-4.55151515151517</v>
       </c>
       <c r="F411" t="n">
-        <v>0.414176356976547</v>
+        <v>0.414176356976543</v>
       </c>
       <c r="G411" t="n">
         <v>19.394214582036</v>
@@ -12453,19 +12453,19 @@
         <v>12.3575757575758</v>
       </c>
       <c r="D412" t="n">
-        <v>0.0000360688682314967</v>
+        <v>0.0000360688682314966</v>
       </c>
       <c r="E412" t="n">
-        <v>9.20606060606062</v>
+        <v>9.20606060606061</v>
       </c>
       <c r="F412" t="n">
-        <v>0.0702004425763711</v>
+        <v>0.0702004425763716</v>
       </c>
       <c r="G412" t="n">
         <v>11.173041044159</v>
       </c>
       <c r="H412" t="n">
-        <v>0.000523863926095</v>
+        <v>0.000523863926094996</v>
       </c>
       <c r="I412" t="s">
         <v>15</v>
@@ -12514,7 +12514,7 @@
         <v>1</v>
       </c>
       <c r="E414" t="n">
-        <v>-0.478787878787878</v>
+        <v>-0.478787878787879</v>
       </c>
       <c r="F414" t="n">
         <v>0.856240346206871</v>
@@ -12659,10 +12659,10 @@
         <v>1</v>
       </c>
       <c r="E419" t="n">
-        <v>1.21212121212121</v>
+        <v>1.21212121212122</v>
       </c>
       <c r="F419" t="n">
-        <v>0.305510588670457</v>
+        <v>0.305510588670451</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -12801,19 +12801,19 @@
         <v>12.2060606060606</v>
       </c>
       <c r="D424" t="n">
-        <v>0.000343191367324596</v>
+        <v>0.000343191367324594</v>
       </c>
       <c r="E424" t="n">
-        <v>1.35757575757575</v>
+        <v>1.35757575757574</v>
       </c>
       <c r="F424" t="n">
-        <v>0.718425706036212</v>
+        <v>0.718425706036213</v>
       </c>
       <c r="G424" t="n">
         <v>12.0098182920622</v>
       </c>
       <c r="H424" t="n">
-        <v>0.000804811525253942</v>
+        <v>0.000804811525253938</v>
       </c>
       <c r="I424" t="s">
         <v>15</v>
@@ -12833,7 +12833,7 @@
         <v>0.00185172617562544</v>
       </c>
       <c r="E425" t="n">
-        <v>-19.9757575757576</v>
+        <v>-19.9757575757575</v>
       </c>
       <c r="F425" t="n">
         <v>0.0159024736446508</v>
@@ -12865,7 +12865,7 @@
         <v>-30.2242424242424</v>
       </c>
       <c r="F426" t="n">
-        <v>0.00534619535093904</v>
+        <v>0.00534619535093906</v>
       </c>
       <c r="G426" t="n">
         <v>16.043617515019</v>
@@ -12888,13 +12888,13 @@
         <v>20.6909090909091</v>
       </c>
       <c r="D427" t="n">
-        <v>0.0315782863883735</v>
+        <v>0.031578286388373</v>
       </c>
       <c r="E427" t="n">
-        <v>-62.4909090909086</v>
+        <v>-62.4909090909087</v>
       </c>
       <c r="F427" t="n">
-        <v>0.00228207718943998</v>
+        <v>0.00228207718944</v>
       </c>
       <c r="G427" t="n">
         <v>49.1642478220559</v>
@@ -12917,13 +12917,13 @@
         <v>3.69696969696969</v>
       </c>
       <c r="D428" t="n">
-        <v>0.0259574838091458</v>
+        <v>0.0259574838091457</v>
       </c>
       <c r="E428" t="n">
-        <v>-2.42424242424243</v>
+        <v>-2.42424242424244</v>
       </c>
       <c r="F428" t="n">
-        <v>0.165690206380445</v>
+        <v>0.165690206380444</v>
       </c>
       <c r="G428" t="n">
         <v>2.47898793078376</v>
@@ -12946,7 +12946,7 @@
         <v>420.8</v>
       </c>
       <c r="D429" t="n">
-        <v>0.0000395092686566696</v>
+        <v>0.0000395092686566694</v>
       </c>
       <c r="E429" t="n">
         <v>-206.157575757575</v>
@@ -12958,7 +12958,7 @@
         <v>597.021112433619</v>
       </c>
       <c r="H429" t="n">
-        <v>0.00000787424714185256</v>
+        <v>0.00000787424714185261</v>
       </c>
       <c r="I429" t="s">
         <v>15</v>
@@ -12981,13 +12981,13 @@
         <v>-10.6909090909091</v>
       </c>
       <c r="F430" t="n">
-        <v>0.00204557552984782</v>
+        <v>0.00204557552984783</v>
       </c>
       <c r="G430" t="n">
         <v>21.4150459687684</v>
       </c>
       <c r="H430" t="n">
-        <v>0.00794029919935586</v>
+        <v>0.00794029919935584</v>
       </c>
       <c r="I430" t="s">
         <v>15</v>
@@ -13001,13 +13001,13 @@
         <v>19</v>
       </c>
       <c r="C431" t="n">
-        <v>4.72727272727272</v>
+        <v>4.72727272727273</v>
       </c>
       <c r="D431" t="n">
-        <v>0.00229144047964162</v>
+        <v>0.00229144047964161</v>
       </c>
       <c r="E431" t="n">
-        <v>-5.64242424242423</v>
+        <v>-5.64242424242422</v>
       </c>
       <c r="F431" t="n">
         <v>0.133772659527786</v>
@@ -13016,7 +13016,7 @@
         <v>4.36960700555318</v>
       </c>
       <c r="H431" t="n">
-        <v>0.0123721144833815</v>
+        <v>0.0123721144833814</v>
       </c>
       <c r="I431" t="s">
         <v>15</v>
@@ -13065,7 +13065,7 @@
         <v>1</v>
       </c>
       <c r="E433" t="n">
-        <v>-3.69696969696969</v>
+        <v>-3.6969696969697</v>
       </c>
       <c r="F433" t="n">
         <v>0.0246146052040661</v>
@@ -13091,7 +13091,7 @@
         <v>5.93939393939394</v>
       </c>
       <c r="D434" t="n">
-        <v>0.00497416886900569</v>
+        <v>0.0049741688690057</v>
       </c>
       <c r="E434" t="n">
         <v>-3.93333333333336</v>
@@ -13126,7 +13126,7 @@
         <v>-1.8</v>
       </c>
       <c r="F435" t="n">
-        <v>0.236350721707066</v>
+        <v>0.236350721707067</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -13178,13 +13178,13 @@
         <v>42.9393939393939</v>
       </c>
       <c r="D437" t="n">
-        <v>0.000289127738338176</v>
+        <v>0.000289127738338175</v>
       </c>
       <c r="E437" t="n">
-        <v>-32.4424242424242</v>
+        <v>-32.4424242424243</v>
       </c>
       <c r="F437" t="n">
-        <v>0.0552308855022075</v>
+        <v>0.0552308855022076</v>
       </c>
       <c r="G437" t="n">
         <v>52.8496833364463</v>
@@ -13213,13 +13213,13 @@
         <v>-12.7636363636364</v>
       </c>
       <c r="F438" t="n">
-        <v>0.00193745181703301</v>
+        <v>0.00193745181703302</v>
       </c>
       <c r="G438" t="n">
         <v>7.89192425585347</v>
       </c>
       <c r="H438" t="n">
-        <v>0.0345132819379154</v>
+        <v>0.0345132819379153</v>
       </c>
       <c r="I438" t="s">
         <v>15</v>
@@ -13242,7 +13242,7 @@
         <v>-12.4121212121212</v>
       </c>
       <c r="F439" t="n">
-        <v>0.000871339841739243</v>
+        <v>0.000871339841739244</v>
       </c>
       <c r="G439" t="n">
         <v>0</v>
@@ -13268,7 +13268,7 @@
         <v>1</v>
       </c>
       <c r="E440" t="n">
-        <v>0.187878787878785</v>
+        <v>0.187878787878787</v>
       </c>
       <c r="F440" t="n">
         <v>0.958539929625203</v>
@@ -13294,19 +13294,19 @@
         <v>15.1939393939394</v>
       </c>
       <c r="D441" t="n">
-        <v>0.000239776102134752</v>
+        <v>0.000239776102134753</v>
       </c>
       <c r="E441" t="n">
-        <v>-4.57575757575754</v>
+        <v>-4.57575757575756</v>
       </c>
       <c r="F441" t="n">
-        <v>0.240975141061758</v>
+        <v>0.240975141061756</v>
       </c>
       <c r="G441" t="n">
         <v>17.5113669010092</v>
       </c>
       <c r="H441" t="n">
-        <v>0.0000316918056401092</v>
+        <v>0.000031691805640109</v>
       </c>
       <c r="I441" t="s">
         <v>15</v>
@@ -13358,7 +13358,7 @@
         <v>-1.16363636363636</v>
       </c>
       <c r="F443" t="n">
-        <v>0.129386654829626</v>
+        <v>0.129386654829627</v>
       </c>
       <c r="G443" t="n">
         <v>0</v>
@@ -13381,13 +13381,13 @@
         <v>6.10909090909091</v>
       </c>
       <c r="D444" t="n">
-        <v>0.0059834025492557</v>
+        <v>0.00598340254925571</v>
       </c>
       <c r="E444" t="n">
-        <v>-3.81212121212119</v>
+        <v>-3.81212121212121</v>
       </c>
       <c r="F444" t="n">
-        <v>0.312803679544762</v>
+        <v>0.31280367954476</v>
       </c>
       <c r="G444" t="n">
         <v>6.21124681792053</v>
@@ -13410,19 +13410,19 @@
         <v>6.33939393939394</v>
       </c>
       <c r="D445" t="n">
-        <v>0.0141957543014797</v>
+        <v>0.0141957543014796</v>
       </c>
       <c r="E445" t="n">
         <v>13.3030303030303</v>
       </c>
       <c r="F445" t="n">
-        <v>0.0534193210453745</v>
+        <v>0.0534193210453747</v>
       </c>
       <c r="G445" t="n">
         <v>3.80405716768241</v>
       </c>
       <c r="H445" t="n">
-        <v>0.145024300389552</v>
+        <v>0.145024300389551</v>
       </c>
       <c r="I445" t="s">
         <v>15</v>
@@ -13439,19 +13439,19 @@
         <v>102.133333333333</v>
       </c>
       <c r="D446" t="n">
-        <v>0.000331380286887992</v>
+        <v>0.000331380286887991</v>
       </c>
       <c r="E446" t="n">
         <v>107.369696969697</v>
       </c>
       <c r="F446" t="n">
-        <v>0.00628319527130978</v>
+        <v>0.00628319527130974</v>
       </c>
       <c r="G446" t="n">
         <v>48.3387343504812</v>
       </c>
       <c r="H446" t="n">
-        <v>0.0164574841395582</v>
+        <v>0.0164574841395583</v>
       </c>
       <c r="I446" t="s">
         <v>15</v>
@@ -13471,16 +13471,16 @@
         <v>0.00206839809483862</v>
       </c>
       <c r="E447" t="n">
-        <v>69.7818181818178</v>
+        <v>69.7818181818177</v>
       </c>
       <c r="F447" t="n">
-        <v>0.0226179405732346</v>
+        <v>0.0226179405732348</v>
       </c>
       <c r="G447" t="n">
-        <v>21.7811824291701</v>
+        <v>21.7811824291702</v>
       </c>
       <c r="H447" t="n">
-        <v>0.0485232055196208</v>
+        <v>0.0485232055196203</v>
       </c>
       <c r="I447" t="s">
         <v>15</v>
@@ -13503,13 +13503,13 @@
         <v>372.684848484848</v>
       </c>
       <c r="F448" t="n">
-        <v>0.00533136372417749</v>
+        <v>0.00533136372417747</v>
       </c>
       <c r="G448" t="n">
         <v>49.0961218926512</v>
       </c>
       <c r="H448" t="n">
-        <v>0.203303880755856</v>
+        <v>0.203303880755857</v>
       </c>
       <c r="I448" t="s">
         <v>11</v>
@@ -13526,19 +13526,19 @@
         <v>39.8969696969697</v>
       </c>
       <c r="D449" t="n">
-        <v>0.0000564073922101956</v>
+        <v>0.0000564073922101961</v>
       </c>
       <c r="E449" t="n">
-        <v>83.6727272727273</v>
+        <v>83.6727272727274</v>
       </c>
       <c r="F449" t="n">
-        <v>0.00404655824447197</v>
+        <v>0.00404655824447194</v>
       </c>
       <c r="G449" t="n">
         <v>27.5563248150988</v>
       </c>
       <c r="H449" t="n">
-        <v>0.00864484130205591</v>
+        <v>0.00864484130205607</v>
       </c>
       <c r="I449" t="s">
         <v>15</v>
@@ -13555,19 +13555,19 @@
         <v>107.709090909091</v>
       </c>
       <c r="D450" t="n">
-        <v>0.000075813007572258</v>
+        <v>0.0000758130075722583</v>
       </c>
       <c r="E450" t="n">
-        <v>89.4545454545454</v>
+        <v>89.4545454545455</v>
       </c>
       <c r="F450" t="n">
-        <v>0.00577841648094405</v>
+        <v>0.00577841648094403</v>
       </c>
       <c r="G450" t="n">
-        <v>59.9197513616878</v>
+        <v>59.9197513616877</v>
       </c>
       <c r="H450" t="n">
-        <v>0.00172783266000535</v>
+        <v>0.00172783266000536</v>
       </c>
       <c r="I450" t="s">
         <v>15</v>
@@ -13584,19 +13584,19 @@
         <v>32.4909090909091</v>
       </c>
       <c r="D451" t="n">
-        <v>0.00113784666805606</v>
+        <v>0.00113784666805607</v>
       </c>
       <c r="E451" t="n">
-        <v>0.490909090909114</v>
+        <v>0.490909090909102</v>
       </c>
       <c r="F451" t="n">
-        <v>0.933243981928496</v>
+        <v>0.933243981928497</v>
       </c>
       <c r="G451" t="n">
         <v>32.0160215766387</v>
       </c>
       <c r="H451" t="n">
-        <v>0.0000738010299666607</v>
+        <v>0.0000738010299666605</v>
       </c>
       <c r="I451" t="s">
         <v>15</v>
@@ -13613,19 +13613,19 @@
         <v>32.7939393939394</v>
       </c>
       <c r="D452" t="n">
-        <v>0.000445849328075633</v>
+        <v>0.000445849328075631</v>
       </c>
       <c r="E452" t="n">
-        <v>18.0303030303031</v>
+        <v>18.0303030303029</v>
       </c>
       <c r="F452" t="n">
-        <v>0.197746828286885</v>
+        <v>0.197746828286894</v>
       </c>
       <c r="G452" t="n">
-        <v>28.0118509062529</v>
+        <v>28.011850906253</v>
       </c>
       <c r="H452" t="n">
-        <v>0.00142687047806593</v>
+        <v>0.00142687047806587</v>
       </c>
       <c r="I452" t="s">
         <v>15</v>
@@ -13642,19 +13642,19 @@
         <v>2.39393939393939</v>
       </c>
       <c r="D453" t="n">
-        <v>0.0749898317320404</v>
+        <v>0.0749898317320406</v>
       </c>
       <c r="E453" t="n">
-        <v>-1.54545454545454</v>
+        <v>-1.54545454545455</v>
       </c>
       <c r="F453" t="n">
-        <v>0.672529074461875</v>
+        <v>0.672529074461874</v>
       </c>
       <c r="G453" t="n">
         <v>2.55478920060894</v>
       </c>
       <c r="H453" t="n">
-        <v>0.0711696610388432</v>
+        <v>0.0711696610388433</v>
       </c>
       <c r="I453" t="s">
         <v>34</v>
@@ -13671,7 +13671,7 @@
         <v>102.248484848485</v>
       </c>
       <c r="D454" t="n">
-        <v>0.0000688826003895608</v>
+        <v>0.0000688826003895617</v>
       </c>
       <c r="E454" t="n">
         <v>100.866666666667</v>
@@ -13680,10 +13680,10 @@
         <v>0.0218892661802258</v>
       </c>
       <c r="G454" t="n">
-        <v>69.9950828736534</v>
+        <v>69.9950828736533</v>
       </c>
       <c r="H454" t="n">
-        <v>0.000464822327952086</v>
+        <v>0.000464822327952087</v>
       </c>
       <c r="I454" t="s">
         <v>15</v>
@@ -13700,19 +13700,19 @@
         <v>65.5454545454546</v>
       </c>
       <c r="D455" t="n">
-        <v>0.00368826799090541</v>
+        <v>0.0036882679909054</v>
       </c>
       <c r="E455" t="n">
-        <v>121.145454545455</v>
+        <v>121.145454545454</v>
       </c>
       <c r="F455" t="n">
-        <v>0.00207533574029662</v>
+        <v>0.00207533574029673</v>
       </c>
       <c r="G455" t="n">
-        <v>2.8767616812578</v>
+        <v>2.87676168125845</v>
       </c>
       <c r="H455" t="n">
-        <v>0.864213919860312</v>
+        <v>0.864213919860281</v>
       </c>
       <c r="I455" t="s">
         <v>11</v>
@@ -13787,19 +13787,19 @@
         <v>45.2848484848485</v>
       </c>
       <c r="D458" t="n">
-        <v>0.00499332988628984</v>
+        <v>0.00499332988628985</v>
       </c>
       <c r="E458" t="n">
-        <v>74.0303030303031</v>
+        <v>74.030303030303</v>
       </c>
       <c r="F458" t="n">
-        <v>0.0182327779089914</v>
+        <v>0.0182327779089916</v>
       </c>
       <c r="G458" t="n">
         <v>16.6637910701009</v>
       </c>
       <c r="H458" t="n">
-        <v>0.155607348719687</v>
+        <v>0.155607348719685</v>
       </c>
       <c r="I458" t="s">
         <v>11</v>
@@ -13822,13 +13822,13 @@
         <v>36.7272727272727</v>
       </c>
       <c r="F459" t="n">
-        <v>0.0288642179293702</v>
+        <v>0.02886421792937</v>
       </c>
       <c r="G459" t="n">
         <v>21.5963043548558</v>
       </c>
       <c r="H459" t="n">
-        <v>0.0185662250021303</v>
+        <v>0.0185662250021304</v>
       </c>
       <c r="I459" t="s">
         <v>15</v>
@@ -13848,10 +13848,10 @@
         <v>0.0180189465476776</v>
       </c>
       <c r="E460" t="n">
-        <v>4.76969696969716</v>
+        <v>4.76969696969718</v>
       </c>
       <c r="F460" t="n">
-        <v>0.781264499889862</v>
+        <v>0.781264499889861</v>
       </c>
       <c r="G460" t="n">
         <v>17.1413130499072</v>
@@ -13871,16 +13871,16 @@
         <v>28</v>
       </c>
       <c r="C461" t="n">
-        <v>70.1393939393939</v>
+        <v>70.139393939394</v>
       </c>
       <c r="D461" t="n">
-        <v>0.000983751702567376</v>
+        <v>0.000983751702567367</v>
       </c>
       <c r="E461" t="n">
         <v>117.381818181818</v>
       </c>
       <c r="F461" t="n">
-        <v>0.00494224817808418</v>
+        <v>0.00494224817808413</v>
       </c>
       <c r="G461" t="n">
         <v>28.4238998546741</v>
@@ -13900,10 +13900,10 @@
         <v>29</v>
       </c>
       <c r="C462" t="n">
-        <v>36.3515151515151</v>
+        <v>36.3515151515152</v>
       </c>
       <c r="D462" t="n">
-        <v>0.000203082502352759</v>
+        <v>0.000203082502352757</v>
       </c>
       <c r="E462" t="n">
         <v>13.290909090909</v>
@@ -13915,7 +13915,7 @@
         <v>32.8062040948064</v>
       </c>
       <c r="H462" t="n">
-        <v>0.0000111799603638529</v>
+        <v>0.000011179960363853</v>
       </c>
       <c r="I462" t="s">
         <v>15</v>
@@ -13935,16 +13935,16 @@
         <v>0.00153013105170411</v>
       </c>
       <c r="E463" t="n">
-        <v>2.00000000000002</v>
+        <v>2</v>
       </c>
       <c r="F463" t="n">
-        <v>0.67629718304808</v>
+        <v>0.676297183048083</v>
       </c>
       <c r="G463" t="n">
-        <v>10.0732866973781</v>
+        <v>10.0732866973782</v>
       </c>
       <c r="H463" t="n">
-        <v>0.00214056575512152</v>
+        <v>0.00214056575512151</v>
       </c>
       <c r="I463" t="s">
         <v>15</v>
@@ -13961,7 +13961,7 @@
         <v>2.74545454545455</v>
       </c>
       <c r="D464" t="n">
-        <v>0.0532035170307896</v>
+        <v>0.0532035170307898</v>
       </c>
       <c r="E464" t="n">
         <v>-16.4060606060606</v>
@@ -13990,19 +13990,19 @@
         <v>24.9515151515152</v>
       </c>
       <c r="D465" t="n">
-        <v>0.0013446371593359</v>
+        <v>0.00134463715933589</v>
       </c>
       <c r="E465" t="n">
         <v>51.6545454545455</v>
       </c>
       <c r="F465" t="n">
-        <v>0.00399197871153882</v>
+        <v>0.00399197871153884</v>
       </c>
       <c r="G465" t="n">
         <v>22.0505538762451</v>
       </c>
       <c r="H465" t="n">
-        <v>0.053420481568526</v>
+        <v>0.0534204815685259</v>
       </c>
       <c r="I465" t="s">
         <v>11</v>
@@ -14080,10 +14080,10 @@
         <v>1</v>
       </c>
       <c r="E468" t="n">
-        <v>0.430303030303028</v>
+        <v>0.43030303030303</v>
       </c>
       <c r="F468" t="n">
-        <v>0.641087848562731</v>
+        <v>0.64108784856273</v>
       </c>
       <c r="G468" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
         <v>4.89090909090908</v>
       </c>
       <c r="F469" t="n">
-        <v>0.0513508233244635</v>
+        <v>0.0513508233244634</v>
       </c>
       <c r="G469" t="n">
         <v>0</v>
@@ -14138,10 +14138,10 @@
         <v>1</v>
       </c>
       <c r="E470" t="n">
-        <v>0.703030303030302</v>
+        <v>0.703030303030301</v>
       </c>
       <c r="F470" t="n">
-        <v>0.344784906517913</v>
+        <v>0.344784906517914</v>
       </c>
       <c r="G470" t="n">
         <v>0</v>
@@ -14167,13 +14167,13 @@
         <v>0.110887997327108</v>
       </c>
       <c r="E471" t="n">
-        <v>-1.33333333333333</v>
+        <v>-1.33333333333334</v>
       </c>
       <c r="F471" t="n">
-        <v>0.698849745196778</v>
+        <v>0.698849745196775</v>
       </c>
       <c r="G471" t="n">
-        <v>1.63446900448729</v>
+        <v>1.63446900448728</v>
       </c>
       <c r="H471" t="n">
         <v>0.130092376542908</v>
@@ -14199,7 +14199,7 @@
         <v>-1.98787878787879</v>
       </c>
       <c r="F472" t="n">
-        <v>0.174689413650455</v>
+        <v>0.174689413650456</v>
       </c>
       <c r="G472" t="n">
         <v>0</v>
@@ -14399,10 +14399,10 @@
         <v>1</v>
       </c>
       <c r="E479" t="n">
-        <v>-2.24848484848485</v>
+        <v>-2.24848484848484</v>
       </c>
       <c r="F479" t="n">
-        <v>0.224664720514798</v>
+        <v>0.224664720514799</v>
       </c>
       <c r="G479" t="n">
         <v>0</v>
@@ -14486,10 +14486,10 @@
         <v>1</v>
       </c>
       <c r="E482" t="n">
-        <v>-0.060606060606064</v>
+        <v>-0.0606060606060605</v>
       </c>
       <c r="F482" t="n">
-        <v>0.960321083418836</v>
+        <v>0.960321083418839</v>
       </c>
       <c r="G482" t="n">
         <v>0</v>
@@ -14518,7 +14518,7 @@
         <v>1.84848484848485</v>
       </c>
       <c r="F483" t="n">
-        <v>0.253988001757586</v>
+        <v>0.253988001757585</v>
       </c>
       <c r="G483" t="n">
         <v>0</v>
@@ -14718,10 +14718,10 @@
         <v>1</v>
       </c>
       <c r="E490" t="n">
-        <v>-0.50909090909091</v>
+        <v>-0.509090909090906</v>
       </c>
       <c r="F490" t="n">
-        <v>0.45618900847831</v>
+        <v>0.456189008478313</v>
       </c>
       <c r="G490" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1.44848484848485</v>
       </c>
       <c r="F491" t="n">
-        <v>0.477454397391084</v>
+        <v>0.477454397391085</v>
       </c>
       <c r="G491" t="n">
         <v>0</v>
@@ -14770,7 +14770,7 @@
         <v>17</v>
       </c>
       <c r="C492" t="n">
-        <v>2.23030303030303</v>
+        <v>2.23030303030304</v>
       </c>
       <c r="D492" t="n">
         <v>0.922761185768913</v>
@@ -14779,13 +14779,13 @@
         <v>-339.848484848485</v>
       </c>
       <c r="F492" t="n">
-        <v>0.00929368375203443</v>
+        <v>0.00929368375203445</v>
       </c>
       <c r="G492" t="n">
         <v>73.8980106570615</v>
       </c>
       <c r="H492" t="n">
-        <v>0.000530806003520483</v>
+        <v>0.000530806003520485</v>
       </c>
       <c r="I492" t="s">
         <v>15</v>
@@ -14837,10 +14837,10 @@
         <v>-66.1878787878788</v>
       </c>
       <c r="F494" t="n">
-        <v>0.000127348083110174</v>
+        <v>0.000127348083110175</v>
       </c>
       <c r="G494" t="n">
-        <v>4.1447000375206</v>
+        <v>4.14470003752059</v>
       </c>
       <c r="H494" t="n">
         <v>0.336085510008885</v>
@@ -15008,10 +15008,10 @@
         <v>1</v>
       </c>
       <c r="E500" t="n">
-        <v>-4.27272727272727</v>
+        <v>-4.27272727272728</v>
       </c>
       <c r="F500" t="n">
-        <v>0.000643790603100208</v>
+        <v>0.000643790603100207</v>
       </c>
       <c r="G500" t="n">
         <v>0</v>
@@ -15092,10 +15092,10 @@
         <v>25.3757575757576</v>
       </c>
       <c r="D503" t="n">
-        <v>0.0000659013412621294</v>
+        <v>0.0000659013412621298</v>
       </c>
       <c r="E503" t="n">
-        <v>2.22424242424251</v>
+        <v>2.22424242424252</v>
       </c>
       <c r="F503" t="n">
         <v>0.91049615303814</v>
@@ -15104,7 +15104,7 @@
         <v>25.0711979141578</v>
       </c>
       <c r="H503" t="n">
-        <v>0.0000102410660115653</v>
+        <v>0.0000102410660115654</v>
       </c>
       <c r="I503" t="s">
         <v>15</v>
@@ -15121,19 +15121,19 @@
         <v>9.86060606060606</v>
       </c>
       <c r="D504" t="n">
-        <v>0.000405768900104802</v>
+        <v>0.000405768900104803</v>
       </c>
       <c r="E504" t="n">
         <v>16.8969696969697</v>
       </c>
       <c r="F504" t="n">
-        <v>0.0255274180102116</v>
+        <v>0.0255274180102115</v>
       </c>
       <c r="G504" t="n">
         <v>7.50422122121495</v>
       </c>
       <c r="H504" t="n">
-        <v>0.0108539599832924</v>
+        <v>0.0108539599832925</v>
       </c>
       <c r="I504" t="s">
         <v>15</v>
@@ -15156,13 +15156,13 @@
         <v>1864.93939393939</v>
       </c>
       <c r="F505" t="n">
-        <v>0.135855274838766</v>
+        <v>0.135855274838767</v>
       </c>
       <c r="G505" t="n">
         <v>-2705.25003211114</v>
       </c>
       <c r="H505" t="n">
-        <v>0.0000000000228176203528899</v>
+        <v>0.0000000000228176203528896</v>
       </c>
       <c r="I505" t="s">
         <v>37</v>
@@ -15205,16 +15205,16 @@
         <v>32</v>
       </c>
       <c r="C507" t="n">
-        <v>7.53939393939393</v>
+        <v>7.53939393939392</v>
       </c>
       <c r="D507" t="n">
-        <v>0.19586980816417</v>
+        <v>0.195869808164171</v>
       </c>
       <c r="E507" t="n">
         <v>-174.181818181818</v>
       </c>
       <c r="F507" t="n">
-        <v>0.00772851545578873</v>
+        <v>0.00772851545578876</v>
       </c>
       <c r="G507" t="n">
         <v>25.2610872576364</v>
@@ -15240,10 +15240,10 @@
         <v>1</v>
       </c>
       <c r="E508" t="n">
-        <v>1.98787878787879</v>
+        <v>1.98787878787878</v>
       </c>
       <c r="F508" t="n">
-        <v>0.263786138468321</v>
+        <v>0.263786138468323</v>
       </c>
       <c r="G508" t="n">
         <v>0</v>
@@ -15269,10 +15269,10 @@
         <v>1</v>
       </c>
       <c r="E509" t="n">
-        <v>-1.52121212121212</v>
+        <v>-1.52121212121213</v>
       </c>
       <c r="F509" t="n">
-        <v>0.363620980208249</v>
+        <v>0.363620980208248</v>
       </c>
       <c r="G509" t="n">
         <v>0</v>
@@ -15298,16 +15298,16 @@
         <v>0.0372798534520337</v>
       </c>
       <c r="E510" t="n">
-        <v>-1.38181818181817</v>
+        <v>-1.38181818181816</v>
       </c>
       <c r="F510" t="n">
-        <v>0.63697656850938</v>
+        <v>0.636976568509381</v>
       </c>
       <c r="G510" t="n">
         <v>-2.90981265921191</v>
       </c>
       <c r="H510" t="n">
-        <v>0.0588581035477896</v>
+        <v>0.0588581035477897</v>
       </c>
       <c r="I510" t="s">
         <v>37</v>
@@ -15327,16 +15327,16 @@
         <v>0.000367847313115613</v>
       </c>
       <c r="E511" t="n">
-        <v>-36.9272727272729</v>
+        <v>-36.9272727272727</v>
       </c>
       <c r="F511" t="n">
-        <v>0.0391790495463569</v>
+        <v>0.0391790495463572</v>
       </c>
       <c r="G511" t="n">
         <v>-34.6558908587646</v>
       </c>
       <c r="H511" t="n">
-        <v>0.00646258302029462</v>
+        <v>0.00646258302029459</v>
       </c>
       <c r="I511" t="s">
         <v>37</v>
@@ -15379,19 +15379,19 @@
         <v>17</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.309090909090911</v>
+        <v>-0.309090909090909</v>
       </c>
       <c r="D513" t="n">
         <v>0.853775253860326</v>
       </c>
       <c r="E513" t="n">
-        <v>-7.02424242424244</v>
+        <v>-7.02424242424242</v>
       </c>
       <c r="F513" t="n">
         <v>0.203942256079512</v>
       </c>
       <c r="G513" t="n">
-        <v>0.148657500135333</v>
+        <v>0.148657500135332</v>
       </c>
       <c r="H513" t="n">
         <v>0.939567313456323</v>
@@ -15469,7 +15469,7 @@
         <v>-8.72727272727273</v>
       </c>
       <c r="D516" t="n">
-        <v>0.0000485077263856957</v>
+        <v>0.0000485077263856958</v>
       </c>
       <c r="E516" t="n">
         <v>-11.2848484848485</v>
@@ -15504,7 +15504,7 @@
         <v>1.23030303030303</v>
       </c>
       <c r="F517" t="n">
-        <v>0.524304413725223</v>
+        <v>0.524304413725224</v>
       </c>
       <c r="G517" t="n">
         <v>0</v>
@@ -15530,16 +15530,16 @@
         <v>0.0029719185630069</v>
       </c>
       <c r="E518" t="n">
-        <v>-7.20606060606073</v>
+        <v>-7.20606060606064</v>
       </c>
       <c r="F518" t="n">
-        <v>0.283288768123148</v>
+        <v>0.283288768123152</v>
       </c>
       <c r="G518" t="n">
-        <v>-8.53490501505178</v>
+        <v>-8.53490501505179</v>
       </c>
       <c r="H518" t="n">
-        <v>0.00544834700585233</v>
+        <v>0.00544834700585225</v>
       </c>
       <c r="I518" t="s">
         <v>37</v>
@@ -15611,22 +15611,22 @@
         <v>25</v>
       </c>
       <c r="C521" t="n">
-        <v>-8.0060606060606</v>
+        <v>-8.00606060606061</v>
       </c>
       <c r="D521" t="n">
-        <v>0.00360982852115638</v>
+        <v>0.00360982852115639</v>
       </c>
       <c r="E521" t="n">
         <v>-1.67272727272728</v>
       </c>
       <c r="F521" t="n">
-        <v>0.395872516415977</v>
+        <v>0.395872516415975</v>
       </c>
       <c r="G521" t="n">
         <v>-7.0991495790152</v>
       </c>
       <c r="H521" t="n">
-        <v>0.00721912794336707</v>
+        <v>0.0072191279433671</v>
       </c>
       <c r="I521" t="s">
         <v>37</v>
@@ -15704,16 +15704,16 @@
         <v>0.0000242257439031553</v>
       </c>
       <c r="E524" t="n">
-        <v>-9.72727272727272</v>
+        <v>-9.72727272727283</v>
       </c>
       <c r="F524" t="n">
-        <v>0.18155671869106</v>
+        <v>0.181556718691057</v>
       </c>
       <c r="G524" t="n">
         <v>-14.8104349853326</v>
       </c>
       <c r="H524" t="n">
-        <v>0.000116753185211913</v>
+        <v>0.000116753185211915</v>
       </c>
       <c r="I524" t="s">
         <v>37</v>
@@ -15736,13 +15736,13 @@
         <v>-15.5818181818181</v>
       </c>
       <c r="F525" t="n">
-        <v>0.00709197266754195</v>
+        <v>0.00709197266754193</v>
       </c>
       <c r="G525" t="n">
-        <v>-2.3744822028233</v>
+        <v>-2.37448220282329</v>
       </c>
       <c r="H525" t="n">
-        <v>0.437876928835427</v>
+        <v>0.437876928835428</v>
       </c>
       <c r="I525" t="s">
         <v>11</v>
@@ -15820,7 +15820,7 @@
         <v>0.0691407908321747</v>
       </c>
       <c r="E528" t="n">
-        <v>-7.8060606060606</v>
+        <v>-7.80606060606061</v>
       </c>
       <c r="F528" t="n">
         <v>0.0511684628584534</v>
@@ -15901,22 +15901,22 @@
         <v>13</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.478787878787878</v>
+        <v>-0.478787878787874</v>
       </c>
       <c r="D531" t="n">
-        <v>0.790841523902245</v>
+        <v>0.790841523902247</v>
       </c>
       <c r="E531" t="n">
-        <v>1.230303030303</v>
+        <v>1.23030303030303</v>
       </c>
       <c r="F531" t="n">
-        <v>0.769474657619997</v>
+        <v>0.769474657619991</v>
       </c>
       <c r="G531" t="n">
-        <v>-0.531668982963505</v>
+        <v>-0.531668982963502</v>
       </c>
       <c r="H531" t="n">
-        <v>0.784132960664518</v>
+        <v>0.784132960664519</v>
       </c>
       <c r="I531" t="s">
         <v>34</v>
@@ -15933,19 +15933,19 @@
         <v>3.84848484848485</v>
       </c>
       <c r="D532" t="n">
-        <v>0.123687164329535</v>
+        <v>0.123687164329536</v>
       </c>
       <c r="E532" t="n">
-        <v>6.53333333333334</v>
+        <v>6.53333333333336</v>
       </c>
       <c r="F532" t="n">
-        <v>0.355577904247455</v>
+        <v>0.355577904247454</v>
       </c>
       <c r="G532" t="n">
-        <v>2.42396635557931</v>
+        <v>2.4239663555793</v>
       </c>
       <c r="H532" t="n">
-        <v>0.24824458183512</v>
+        <v>0.248244581835122</v>
       </c>
       <c r="I532" t="s">
         <v>34</v>
@@ -15997,13 +15997,13 @@
         <v>4.13939393939394</v>
       </c>
       <c r="F534" t="n">
-        <v>0.0876639428558689</v>
+        <v>0.087663942855868</v>
       </c>
       <c r="G534" t="n">
         <v>2.93729304954646</v>
       </c>
       <c r="H534" t="n">
-        <v>0.372160720339077</v>
+        <v>0.372160720339078</v>
       </c>
       <c r="I534" t="s">
         <v>34</v>
@@ -16049,7 +16049,7 @@
         <v>-2.63030303030303</v>
       </c>
       <c r="D536" t="n">
-        <v>0.000891459589932123</v>
+        <v>0.000891459589932116</v>
       </c>
       <c r="E536" t="n">
         <v>20.7090909090909</v>
@@ -16061,7 +16061,7 @@
         <v>-3.06625036388643</v>
       </c>
       <c r="H536" t="n">
-        <v>0.00200713027126326</v>
+        <v>0.00200713027126325</v>
       </c>
       <c r="I536" t="s">
         <v>37</v>
@@ -16081,10 +16081,10 @@
         <v>1</v>
       </c>
       <c r="E537" t="n">
-        <v>0.26060606060606</v>
+        <v>0.260606060606063</v>
       </c>
       <c r="F537" t="n">
-        <v>0.932470092155773</v>
+        <v>0.932470092155772</v>
       </c>
       <c r="G537" t="n">
         <v>0</v>
@@ -16110,7 +16110,7 @@
         <v>1</v>
       </c>
       <c r="E538" t="n">
-        <v>-0.727272727272726</v>
+        <v>-0.727272727272725</v>
       </c>
       <c r="F538" t="n">
         <v>0.443294315974283</v>
@@ -16139,13 +16139,13 @@
         <v>0.666752443579225</v>
       </c>
       <c r="E539" t="n">
-        <v>9.87272727272729</v>
+        <v>9.8727272727273</v>
       </c>
       <c r="F539" t="n">
-        <v>0.34963726412802</v>
+        <v>0.349637264128019</v>
       </c>
       <c r="G539" t="n">
-        <v>-0.874082149086027</v>
+        <v>-0.874082149086026</v>
       </c>
       <c r="H539" t="n">
         <v>0.772003240247442</v>
@@ -16171,7 +16171,7 @@
         <v>-3.14545454545454</v>
       </c>
       <c r="F540" t="n">
-        <v>0.0923707650758111</v>
+        <v>0.0923707650758113</v>
       </c>
       <c r="G540" t="n">
         <v>0</v>
@@ -16223,7 +16223,7 @@
         <v>12.5151515151515</v>
       </c>
       <c r="D542" t="n">
-        <v>0.22629392284885</v>
+        <v>0.226293922848852</v>
       </c>
       <c r="E542" t="n">
         <v>46.4242424242426</v>
@@ -16232,10 +16232,10 @@
         <v>0.134470873453217</v>
       </c>
       <c r="G542" t="n">
-        <v>1.09284180661173</v>
+        <v>1.09284180661165</v>
       </c>
       <c r="H542" t="n">
-        <v>0.898191475959047</v>
+        <v>0.898191475959053</v>
       </c>
       <c r="I542" t="s">
         <v>34</v>
@@ -16310,19 +16310,19 @@
         <v>1.23030303030303</v>
       </c>
       <c r="D545" t="n">
-        <v>0.354434507647279</v>
+        <v>0.354434507647278</v>
       </c>
       <c r="E545" t="n">
-        <v>11.9151515151515</v>
+        <v>11.9151515151516</v>
       </c>
       <c r="F545" t="n">
-        <v>0.0629876817440427</v>
+        <v>0.0629876817440405</v>
       </c>
       <c r="G545" t="n">
         <v>1.6425679058159</v>
       </c>
       <c r="H545" t="n">
-        <v>0.356296699134655</v>
+        <v>0.356296699134656</v>
       </c>
       <c r="I545" t="s">
         <v>34</v>
@@ -16339,19 +16339,19 @@
         <v>-44.9151515151515</v>
       </c>
       <c r="D546" t="n">
-        <v>0.0000478919437333691</v>
+        <v>0.0000478919437333692</v>
       </c>
       <c r="E546" t="n">
-        <v>59.4303030303031</v>
+        <v>59.4303030303032</v>
       </c>
       <c r="F546" t="n">
-        <v>0.0334071960259818</v>
+        <v>0.0334071960259816</v>
       </c>
       <c r="G546" t="n">
         <v>-50.3186996610076</v>
       </c>
       <c r="H546" t="n">
-        <v>0.000303966773345529</v>
+        <v>0.000303966773345531</v>
       </c>
       <c r="I546" t="s">
         <v>37</v>
@@ -16490,13 +16490,13 @@
         <v>13.0545454545455</v>
       </c>
       <c r="F551" t="n">
-        <v>0.00939901901578521</v>
+        <v>0.00939901901578517</v>
       </c>
       <c r="G551" t="n">
         <v>3.78999742547881</v>
       </c>
       <c r="H551" t="n">
-        <v>0.0701466623634103</v>
+        <v>0.0701466623634102</v>
       </c>
       <c r="I551" t="s">
         <v>11</v>
@@ -16600,13 +16600,13 @@
         <v>4.61818181818182</v>
       </c>
       <c r="D555" t="n">
-        <v>0.000106724139685748</v>
+        <v>0.000106724139685747</v>
       </c>
       <c r="E555" t="n">
-        <v>0.266666666666673</v>
+        <v>0.266666666666647</v>
       </c>
       <c r="F555" t="n">
-        <v>0.934443473904868</v>
+        <v>0.934443473904874</v>
       </c>
       <c r="G555" t="n">
         <v>4.63771557859443</v>
@@ -16667,7 +16667,7 @@
         <v>0.000840666114385217</v>
       </c>
       <c r="G557" t="n">
-        <v>0.519877292518805</v>
+        <v>0.519877292518807</v>
       </c>
       <c r="H557" t="n">
         <v>0.855265754747574</v>
@@ -16719,10 +16719,10 @@
         <v>1</v>
       </c>
       <c r="E559" t="n">
-        <v>0.933333333333332</v>
+        <v>0.933333333333336</v>
       </c>
       <c r="F559" t="n">
-        <v>0.64480514337636</v>
+        <v>0.644805143376358</v>
       </c>
       <c r="G559" t="n">
         <v>0</v>
@@ -16748,10 +16748,10 @@
         <v>0.000121513704807713</v>
       </c>
       <c r="E560" t="n">
-        <v>4.53939393939393</v>
+        <v>4.53939393939392</v>
       </c>
       <c r="F560" t="n">
-        <v>0.361895314739036</v>
+        <v>0.361895314739037</v>
       </c>
       <c r="G560" t="n">
         <v>11.7345903889245</v>
@@ -16832,7 +16832,7 @@
         <v>7.49090909090909</v>
       </c>
       <c r="D563" t="n">
-        <v>0.0000420452194771811</v>
+        <v>0.0000420452194771809</v>
       </c>
       <c r="E563" t="n">
         <v>12.9818181818182</v>
@@ -16844,7 +16844,7 @@
         <v>6.53903156179107</v>
       </c>
       <c r="H563" t="n">
-        <v>0.00631091325710024</v>
+        <v>0.00631091325710022</v>
       </c>
       <c r="I563" t="s">
         <v>15</v>
@@ -16864,7 +16864,7 @@
         <v>1</v>
       </c>
       <c r="E564" t="n">
-        <v>0.769696969696971</v>
+        <v>0.769696969696972</v>
       </c>
       <c r="F564" t="n">
         <v>0.658763050341109</v>
@@ -16948,7 +16948,7 @@
         <v>7.35757575757576</v>
       </c>
       <c r="D567" t="n">
-        <v>0.0012859616992406</v>
+        <v>0.00128596169924059</v>
       </c>
       <c r="E567" t="n">
         <v>10.3151515151515</v>
@@ -16983,7 +16983,7 @@
         <v>-2.55757575757575</v>
       </c>
       <c r="F568" t="n">
-        <v>0.255646797978769</v>
+        <v>0.25564679797877</v>
       </c>
       <c r="G568" t="n">
         <v>0</v>
@@ -17032,7 +17032,7 @@
         <v>32</v>
       </c>
       <c r="C570" t="n">
-        <v>0.945454545454546</v>
+        <v>0.945454545454545</v>
       </c>
       <c r="D570" t="n">
         <v>0.205492061137638</v>
@@ -17041,7 +17041,7 @@
         <v>10.0787878787879</v>
       </c>
       <c r="F570" t="n">
-        <v>0.000580533413838473</v>
+        <v>0.000580533413838474</v>
       </c>
       <c r="G570" t="n">
         <v>1.64661221064562</v>
@@ -17128,7 +17128,7 @@
         <v>-1.24242424242424</v>
       </c>
       <c r="F573" t="n">
-        <v>0.732566249572197</v>
+        <v>0.732566249572198</v>
       </c>
       <c r="G573" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
         <v>-2.04848484848485</v>
       </c>
       <c r="F574" t="n">
-        <v>0.478837739511951</v>
+        <v>0.478837739511952</v>
       </c>
       <c r="G574" t="n">
         <v>0</v>
@@ -17554,10 +17554,10 @@
         <v>29</v>
       </c>
       <c r="C588" t="n">
-        <v>1.41212121212121</v>
+        <v>1.41212121212122</v>
       </c>
       <c r="D588" t="n">
-        <v>0.387171474610433</v>
+        <v>0.387171474610431</v>
       </c>
       <c r="E588" t="n">
         <v>-20.7575757575758</v>
@@ -17566,7 +17566,7 @@
         <v>0.0522144575656962</v>
       </c>
       <c r="G588" t="n">
-        <v>3.09409250337047</v>
+        <v>3.09409250337048</v>
       </c>
       <c r="H588" t="n">
         <v>0.140457622790111</v>
@@ -17705,7 +17705,7 @@
         <v>1</v>
       </c>
       <c r="E593" t="n">
-        <v>0.157575757575758</v>
+        <v>0.157575757575757</v>
       </c>
       <c r="F593" t="n">
         <v>0.93194575077175</v>
@@ -17763,10 +17763,10 @@
         <v>1</v>
       </c>
       <c r="E595" t="n">
-        <v>-1.10909090909091</v>
+        <v>-1.1090909090909</v>
       </c>
       <c r="F595" t="n">
-        <v>0.384057223949624</v>
+        <v>0.384057223949625</v>
       </c>
       <c r="G595" t="n">
         <v>0</v>
@@ -18056,7 +18056,7 @@
         <v>1.39393939393939</v>
       </c>
       <c r="F605" t="n">
-        <v>0.0288221871333692</v>
+        <v>0.0288221871333691</v>
       </c>
       <c r="G605" t="n">
         <v>0</v>
@@ -18166,13 +18166,13 @@
         <v>12.0242424242424</v>
       </c>
       <c r="D609" t="n">
-        <v>0.0006134214434001</v>
+        <v>0.000613421443400101</v>
       </c>
       <c r="E609" t="n">
-        <v>-2.34545454545454</v>
+        <v>-2.34545454545453</v>
       </c>
       <c r="F609" t="n">
-        <v>0.430435318176371</v>
+        <v>0.430435318176372</v>
       </c>
       <c r="G609" t="n">
         <v>13.3472227976412</v>
@@ -18366,7 +18366,7 @@
         <v>14</v>
       </c>
       <c r="C616" t="n">
-        <v>8.56363636363637</v>
+        <v>8.56363636363636</v>
       </c>
       <c r="D616" t="n">
         <v>0.0000178937935695975</v>
@@ -18378,10 +18378,10 @@
         <v>0.0274564412613388</v>
       </c>
       <c r="G616" t="n">
-        <v>9.53244251318775</v>
+        <v>9.53244251318774</v>
       </c>
       <c r="H616" t="n">
-        <v>0.000152568709007525</v>
+        <v>0.000152568709007523</v>
       </c>
       <c r="I616" t="s">
         <v>15</v>
@@ -18395,16 +18395,16 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.981818181818179</v>
+        <v>-0.981818181818187</v>
       </c>
       <c r="D617" t="n">
-        <v>0.743308450801422</v>
+        <v>0.74330845080142</v>
       </c>
       <c r="E617" t="n">
         <v>-85.5999999999999</v>
       </c>
       <c r="F617" t="n">
-        <v>0.00329506419373157</v>
+        <v>0.00329506419373158</v>
       </c>
       <c r="G617" t="n">
         <v>8.89196850547259</v>
@@ -18578,7 +18578,7 @@
         <v>-5.50909090909091</v>
       </c>
       <c r="F623" t="n">
-        <v>0.0335269220173815</v>
+        <v>0.0335269220173814</v>
       </c>
       <c r="G623" t="n">
         <v>0</v>
@@ -18778,13 +18778,13 @@
         <v>0.00150175900138155</v>
       </c>
       <c r="E630" t="n">
-        <v>-61.1515151515152</v>
+        <v>-61.1515151515151</v>
       </c>
       <c r="F630" t="n">
-        <v>0.0557021252334679</v>
+        <v>0.055702125233468</v>
       </c>
       <c r="G630" t="n">
-        <v>7.82772651660495</v>
+        <v>7.82772651660494</v>
       </c>
       <c r="H630" t="n">
         <v>0.0116384213846737</v>
@@ -19045,10 +19045,10 @@
         <v>0.00000169006824622735</v>
       </c>
       <c r="G639" t="n">
-        <v>2.48738715700886</v>
+        <v>2.48738715700952</v>
       </c>
       <c r="H639" t="n">
-        <v>0.983151305393166</v>
+        <v>0.983151305393161</v>
       </c>
       <c r="I639" t="s">
         <v>11</v>
@@ -19271,10 +19271,10 @@
         <v>1</v>
       </c>
       <c r="E647" t="n">
-        <v>2.45454545454546</v>
+        <v>2.45454545454545</v>
       </c>
       <c r="F647" t="n">
-        <v>0.0094618493078961</v>
+        <v>0.00946184930789614</v>
       </c>
       <c r="G647" t="n">
         <v>0</v>
@@ -19477,13 +19477,13 @@
         <v>1474.18181818182</v>
       </c>
       <c r="F654" t="n">
-        <v>0.00000836933084547208</v>
+        <v>0.00000836933084547212</v>
       </c>
       <c r="G654" t="n">
-        <v>-97.7902234253894</v>
+        <v>-97.7902234253891</v>
       </c>
       <c r="H654" t="n">
-        <v>0.0750821156692362</v>
+        <v>0.0750821156692371</v>
       </c>
       <c r="I654" t="s">
         <v>11</v>
@@ -19935,13 +19935,13 @@
         <v>-11.4</v>
       </c>
       <c r="D670" t="n">
-        <v>0.00428521785971911</v>
+        <v>0.00428521785971912</v>
       </c>
       <c r="E670" t="n">
         <v>-123.212121212121</v>
       </c>
       <c r="F670" t="n">
-        <v>0.0000255742181447518</v>
+        <v>0.0000255742181447519</v>
       </c>
       <c r="G670" t="n">
         <v>11.3605185611215</v>
@@ -19996,7 +19996,7 @@
         <v>1</v>
       </c>
       <c r="E672" t="n">
-        <v>-11.4484848484848</v>
+        <v>-11.4484848484849</v>
       </c>
       <c r="F672" t="n">
         <v>0.0000768974162790096</v>
@@ -20028,7 +20028,7 @@
         <v>-53.0969696969698</v>
       </c>
       <c r="F673" t="n">
-        <v>0.0648351622816819</v>
+        <v>0.0648351622816818</v>
       </c>
       <c r="G673" t="n">
         <v>-8.56105959582087</v>
@@ -20260,7 +20260,7 @@
         <v>-1.66060606060606</v>
       </c>
       <c r="F681" t="n">
-        <v>0.190780472402595</v>
+        <v>0.190780472402594</v>
       </c>
       <c r="G681" t="n">
         <v>0</v>
@@ -20579,7 +20579,7 @@
         <v>1.75757575757576</v>
       </c>
       <c r="F692" t="n">
-        <v>0.471342022373518</v>
+        <v>0.471342022373519</v>
       </c>
       <c r="G692" t="n">
         <v>0</v>
@@ -20718,7 +20718,7 @@
         <v>399.448484848485</v>
       </c>
       <c r="D697" t="n">
-        <v>0.000292076388031195</v>
+        <v>0.000292076388031197</v>
       </c>
       <c r="E697" t="n">
         <v>1117.27272727273</v>
@@ -20727,10 +20727,10 @@
         <v>0.000229790156511373</v>
       </c>
       <c r="G697" t="n">
-        <v>109.358447763345</v>
+        <v>109.358447763344</v>
       </c>
       <c r="H697" t="n">
-        <v>0.400807265641735</v>
+        <v>0.400807265641737</v>
       </c>
       <c r="I697" t="s">
         <v>11</v>
@@ -20753,13 +20753,13 @@
         <v>662.060606060607</v>
       </c>
       <c r="F698" t="n">
-        <v>0.00329817394807345</v>
+        <v>0.00329817394807346</v>
       </c>
       <c r="G698" t="n">
         <v>219.982815664442</v>
       </c>
       <c r="H698" t="n">
-        <v>0.00923143376366749</v>
+        <v>0.00923143376366747</v>
       </c>
       <c r="I698" t="s">
         <v>15</v>
@@ -20776,13 +20776,13 @@
         <v>59.2</v>
       </c>
       <c r="D699" t="n">
-        <v>0.00000799857678788517</v>
+        <v>0.00000799857678788514</v>
       </c>
       <c r="E699" t="n">
         <v>87.351515151515</v>
       </c>
       <c r="F699" t="n">
-        <v>0.0164102926049682</v>
+        <v>0.0164102926049681</v>
       </c>
       <c r="G699" t="n">
         <v>45.9051803295611</v>
@@ -20817,7 +20817,7 @@
         <v>291.703451442878</v>
       </c>
       <c r="H700" t="n">
-        <v>0.0000476661430036557</v>
+        <v>0.000047666143003655</v>
       </c>
       <c r="I700" t="s">
         <v>15</v>
@@ -20834,19 +20834,19 @@
         <v>189.072727272727</v>
       </c>
       <c r="D701" t="n">
-        <v>0.0000932594146445587</v>
+        <v>0.0000932594146445588</v>
       </c>
       <c r="E701" t="n">
         <v>968.781818181818</v>
       </c>
       <c r="F701" t="n">
-        <v>0.00375025952253884</v>
+        <v>0.00375025952253883</v>
       </c>
       <c r="G701" t="n">
-        <v>90.7163034016483</v>
+        <v>90.7163034016482</v>
       </c>
       <c r="H701" t="n">
-        <v>0.00170559797673714</v>
+        <v>0.00170559797673715</v>
       </c>
       <c r="I701" t="s">
         <v>15</v>
@@ -20875,7 +20875,7 @@
         <v>3208.87132757683</v>
       </c>
       <c r="H702" t="n">
-        <v>0.0607978653931234</v>
+        <v>0.0607978653931236</v>
       </c>
       <c r="I702" t="s">
         <v>11</v>
@@ -20892,10 +20892,10 @@
         <v>3385.07878787879</v>
       </c>
       <c r="D703" t="n">
-        <v>0.0000261388960074684</v>
+        <v>0.0000261388960074685</v>
       </c>
       <c r="E703" t="n">
-        <v>4296.22424242425</v>
+        <v>4296.22424242424</v>
       </c>
       <c r="F703" t="n">
         <v>0.00369168556836268</v>
@@ -20904,7 +20904,7 @@
         <v>2097.10837809803</v>
       </c>
       <c r="H703" t="n">
-        <v>0.00190810354689971</v>
+        <v>0.00190810354689972</v>
       </c>
       <c r="I703" t="s">
         <v>15</v>
@@ -20927,13 +20927,13 @@
         <v>499.115151515152</v>
       </c>
       <c r="F704" t="n">
-        <v>0.000258759824287962</v>
+        <v>0.000258759824287963</v>
       </c>
       <c r="G704" t="n">
-        <v>85.064764109862</v>
+        <v>85.0647641098618</v>
       </c>
       <c r="H704" t="n">
-        <v>0.0209847354534728</v>
+        <v>0.0209847354534726</v>
       </c>
       <c r="I704" t="s">
         <v>15</v>
@@ -20959,10 +20959,10 @@
         <v>0.000315683694983403</v>
       </c>
       <c r="G705" t="n">
-        <v>-16.1883225354788</v>
+        <v>-16.1883225354787</v>
       </c>
       <c r="H705" t="n">
-        <v>0.638925991187405</v>
+        <v>0.638925991187407</v>
       </c>
       <c r="I705" t="s">
         <v>11</v>
@@ -20979,7 +20979,7 @@
         <v>70.7393939393939</v>
       </c>
       <c r="D706" t="n">
-        <v>0.00381081715978708</v>
+        <v>0.00381081715978707</v>
       </c>
       <c r="E706" t="n">
         <v>275.060606060606</v>
@@ -20988,10 +20988,10 @@
         <v>0.000113470736082277</v>
       </c>
       <c r="G706" t="n">
-        <v>-34.3584746947736</v>
+        <v>-34.3584746947735</v>
       </c>
       <c r="H706" t="n">
-        <v>0.227166838532333</v>
+        <v>0.227166838532334</v>
       </c>
       <c r="I706" t="s">
         <v>11</v>
@@ -21008,7 +21008,7 @@
         <v>797.884848484848</v>
       </c>
       <c r="D707" t="n">
-        <v>0.0000542537755466688</v>
+        <v>0.0000542537755466686</v>
       </c>
       <c r="E707" t="n">
         <v>1974.98181818182</v>
@@ -21020,7 +21020,7 @@
         <v>293.938455844809</v>
       </c>
       <c r="H707" t="n">
-        <v>0.0629142223425559</v>
+        <v>0.0629142223425556</v>
       </c>
       <c r="I707" t="s">
         <v>11</v>
@@ -21043,13 +21043,13 @@
         <v>1809.73333333333</v>
       </c>
       <c r="F708" t="n">
-        <v>0.00175821456040637</v>
+        <v>0.00175821456040638</v>
       </c>
       <c r="G708" t="n">
         <v>648.426198230825</v>
       </c>
       <c r="H708" t="n">
-        <v>0.0600276482158261</v>
+        <v>0.0600276482158256</v>
       </c>
       <c r="I708" t="s">
         <v>11</v>
@@ -21069,10 +21069,10 @@
         <v>1</v>
       </c>
       <c r="E709" t="n">
-        <v>6.45454545454547</v>
+        <v>6.45454545454546</v>
       </c>
       <c r="F709" t="n">
-        <v>0.0784651916505765</v>
+        <v>0.0784651916505767</v>
       </c>
       <c r="G709" t="n">
         <v>0</v>
@@ -21107,7 +21107,7 @@
         <v>326.679390741206</v>
       </c>
       <c r="H710" t="n">
-        <v>0.00851070158212048</v>
+        <v>0.00851070158212047</v>
       </c>
       <c r="I710" t="s">
         <v>15</v>
@@ -21124,19 +21124,19 @@
         <v>130.842424242424</v>
       </c>
       <c r="D711" t="n">
-        <v>0.0000916714599815562</v>
+        <v>0.000091671459981556</v>
       </c>
       <c r="E711" t="n">
         <v>155.842424242424</v>
       </c>
       <c r="F711" t="n">
-        <v>0.0111096212173771</v>
+        <v>0.0111096212173772</v>
       </c>
       <c r="G711" t="n">
-        <v>84.5251678794844</v>
+        <v>84.5251678794843</v>
       </c>
       <c r="H711" t="n">
-        <v>0.00275090800206504</v>
+        <v>0.00275090800206495</v>
       </c>
       <c r="I711" t="s">
         <v>15</v>
@@ -21153,7 +21153,7 @@
         <v>875.10303030303</v>
       </c>
       <c r="D712" t="n">
-        <v>0.0000985006417504404</v>
+        <v>0.0000985006417504403</v>
       </c>
       <c r="E712" t="n">
         <v>1300.3696969697</v>
@@ -21165,7 +21165,7 @@
         <v>396.797618944297</v>
       </c>
       <c r="H712" t="n">
-        <v>0.0235902626085966</v>
+        <v>0.0235902626085967</v>
       </c>
       <c r="I712" t="s">
         <v>15</v>
@@ -21182,19 +21182,19 @@
         <v>1499.67272727273</v>
       </c>
       <c r="D713" t="n">
-        <v>0.0000284475005715317</v>
+        <v>0.0000284475005715316</v>
       </c>
       <c r="E713" t="n">
         <v>5824.8303030303</v>
       </c>
       <c r="F713" t="n">
-        <v>0.0000869907809522731</v>
+        <v>0.0000869907809522726</v>
       </c>
       <c r="G713" t="n">
-        <v>437.261300260455</v>
+        <v>437.261300260451</v>
       </c>
       <c r="H713" t="n">
-        <v>0.177776486472919</v>
+        <v>0.17777648647292</v>
       </c>
       <c r="I713" t="s">
         <v>11</v>
@@ -21214,16 +21214,16 @@
         <v>0.000359027815882068</v>
       </c>
       <c r="E714" t="n">
-        <v>700.454545454547</v>
+        <v>700.454545454546</v>
       </c>
       <c r="F714" t="n">
-        <v>0.000394394397351398</v>
+        <v>0.0003943943973514</v>
       </c>
       <c r="G714" t="n">
         <v>29.319438325268</v>
       </c>
       <c r="H714" t="n">
-        <v>0.519966016567644</v>
+        <v>0.519966016567643</v>
       </c>
       <c r="I714" t="s">
         <v>11</v>
@@ -21240,19 +21240,19 @@
         <v>895.315151515152</v>
       </c>
       <c r="D715" t="n">
-        <v>0.0000272244689560568</v>
+        <v>0.0000272244689560567</v>
       </c>
       <c r="E715" t="n">
         <v>1646.83636363636</v>
       </c>
       <c r="F715" t="n">
-        <v>0.000472933186852075</v>
+        <v>0.000472933186852076</v>
       </c>
       <c r="G715" t="n">
         <v>394.480271784844</v>
       </c>
       <c r="H715" t="n">
-        <v>0.0222169564886147</v>
+        <v>0.0222169564886143</v>
       </c>
       <c r="I715" t="s">
         <v>15</v>
@@ -21269,7 +21269,7 @@
         <v>56.5333333333333</v>
       </c>
       <c r="D716" t="n">
-        <v>0.00000868570817525114</v>
+        <v>0.00000868570817525111</v>
       </c>
       <c r="E716" t="n">
         <v>65.2363636363636</v>
@@ -21281,7 +21281,7 @@
         <v>41.0108217595161</v>
       </c>
       <c r="H716" t="n">
-        <v>0.000394170706007274</v>
+        <v>0.000394170706007271</v>
       </c>
       <c r="I716" t="s">
         <v>15</v>
@@ -21298,7 +21298,7 @@
         <v>1485.38181818182</v>
       </c>
       <c r="D717" t="n">
-        <v>0.000282509209326198</v>
+        <v>0.000282509209326197</v>
       </c>
       <c r="E717" t="n">
         <v>6715.43636363636</v>
@@ -21310,7 +21310,7 @@
         <v>433.336178356625</v>
       </c>
       <c r="H717" t="n">
-        <v>0.0194387902969447</v>
+        <v>0.0194387902969449</v>
       </c>
       <c r="I717" t="s">
         <v>15</v>
